--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_shipbuilding_marine.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08867949977763522</v>
+        <v>0.08849155102819112</v>
       </c>
       <c r="C2">
-        <v>11090.12398626799</v>
+        <v>11006.97758092581</v>
       </c>
       <c r="D2">
-        <v>10418.12398626799</v>
+        <v>10463.98958092581</v>
       </c>
       <c r="E2">
-        <v>-5850.5</v>
+        <v>-5721.488</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>129.012</v>
       </c>
       <c r="G2">
         <v>672</v>
@@ -1579,28 +1579,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.4893036</v>
       </c>
       <c r="N2">
-        <v>830.1749999999998</v>
+        <v>823.6856963999999</v>
       </c>
       <c r="O2">
-        <v>207.54375</v>
+        <v>205.9214241</v>
       </c>
       <c r="P2">
-        <v>622.6312499999999</v>
+        <v>617.7642722999999</v>
       </c>
       <c r="Q2">
-        <v>1022.83125</v>
+        <v>1017.9642723</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08867949977763522</v>
+        <v>0.08900434447292033</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8659731901544416</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>127.9297519690711</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08849155102819112</v>
+        <v>0.08830360227874705</v>
       </c>
       <c r="C3">
-        <v>11006.97758092581</v>
+        <v>10924.23680619827</v>
       </c>
       <c r="D3">
-        <v>10463.98958092581</v>
+        <v>10510.26080619827</v>
       </c>
       <c r="E3">
-        <v>-5721.488</v>
+        <v>-5592.476</v>
       </c>
       <c r="F3">
-        <v>129.012</v>
+        <v>258.024</v>
       </c>
       <c r="G3">
         <v>672</v>
@@ -1661,28 +1661,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M3">
-        <v>6.4893036</v>
+        <v>12.9786072</v>
       </c>
       <c r="N3">
-        <v>823.6856963999999</v>
+        <v>817.1963927999998</v>
       </c>
       <c r="O3">
-        <v>205.9214241</v>
+        <v>204.2990981999999</v>
       </c>
       <c r="P3">
-        <v>617.7642722999999</v>
+        <v>612.8972945999999</v>
       </c>
       <c r="Q3">
-        <v>1017.9642723</v>
+        <v>1013.0972946</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08900434447292033</v>
+        <v>0.08933581865178269</v>
       </c>
       <c r="T3">
-        <v>0.8659731901544416</v>
+        <v>0.8726171458867913</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>127.9297519690711</v>
+        <v>63.96487598453552</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08830360227874705</v>
+        <v>0.08811565352930294</v>
       </c>
       <c r="C4">
-        <v>10924.23680619827</v>
+        <v>10841.90706701904</v>
       </c>
       <c r="D4">
-        <v>10510.26080619827</v>
+        <v>10556.94306701904</v>
       </c>
       <c r="E4">
-        <v>-5592.476</v>
+        <v>-5463.464</v>
       </c>
       <c r="F4">
-        <v>258.024</v>
+        <v>387.036</v>
       </c>
       <c r="G4">
         <v>672</v>
@@ -1743,28 +1743,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M4">
-        <v>12.9786072</v>
+        <v>19.4679108</v>
       </c>
       <c r="N4">
-        <v>817.1963927999998</v>
+        <v>810.7070891999998</v>
       </c>
       <c r="O4">
-        <v>204.2990981999999</v>
+        <v>202.6767723</v>
       </c>
       <c r="P4">
-        <v>612.8972945999999</v>
+        <v>608.0303168999999</v>
       </c>
       <c r="Q4">
-        <v>1013.0972946</v>
+        <v>1008.2303169</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08933581865178269</v>
+        <v>0.08967412734979685</v>
       </c>
       <c r="T4">
-        <v>0.8726171458867913</v>
+        <v>0.8793980903971272</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>63.96487598453552</v>
+        <v>42.64325065635702</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08811565352930294</v>
+        <v>0.08792770477985885</v>
       </c>
       <c r="C5">
-        <v>10841.90706701904</v>
+        <v>10759.99386477617</v>
       </c>
       <c r="D5">
-        <v>10556.94306701904</v>
+        <v>10604.04186477617</v>
       </c>
       <c r="E5">
-        <v>-5463.464</v>
+        <v>-5334.452</v>
       </c>
       <c r="F5">
-        <v>387.036</v>
+        <v>516.048</v>
       </c>
       <c r="G5">
         <v>672</v>
@@ -1825,28 +1825,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M5">
-        <v>19.4679108</v>
+        <v>25.9572144</v>
       </c>
       <c r="N5">
-        <v>810.7070891999998</v>
+        <v>804.2177855999998</v>
       </c>
       <c r="O5">
-        <v>202.6767723</v>
+        <v>201.0544464</v>
       </c>
       <c r="P5">
-        <v>608.0303168999999</v>
+        <v>603.1633391999999</v>
       </c>
       <c r="Q5">
-        <v>1008.2303169</v>
+        <v>1003.3633392</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08967412734979685</v>
+        <v>0.09001948414568631</v>
       </c>
       <c r="T5">
-        <v>0.8793980903971272</v>
+        <v>0.8863203045847622</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.64325065635702</v>
+        <v>31.98243799226777</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08792770477985885</v>
+        <v>0.08773975603041478</v>
       </c>
       <c r="C6">
-        <v>10759.99386477617</v>
+        <v>10678.50279947336</v>
       </c>
       <c r="D6">
-        <v>10604.04186477617</v>
+        <v>10651.56279947336</v>
       </c>
       <c r="E6">
-        <v>-5334.452</v>
+        <v>-5205.44</v>
       </c>
       <c r="F6">
-        <v>516.048</v>
+        <v>645.0600000000001</v>
       </c>
       <c r="G6">
         <v>672</v>
@@ -1907,28 +1907,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M6">
-        <v>25.9572144</v>
+        <v>32.446518</v>
       </c>
       <c r="N6">
-        <v>804.2177855999998</v>
+        <v>797.7284819999999</v>
       </c>
       <c r="O6">
-        <v>201.0544464</v>
+        <v>199.4321205</v>
       </c>
       <c r="P6">
-        <v>603.1633391999999</v>
+        <v>598.2963614999999</v>
       </c>
       <c r="Q6">
-        <v>1003.3633392</v>
+        <v>998.4963614999998</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09001948414568631</v>
+        <v>0.09037211161096292</v>
       </c>
       <c r="T6">
-        <v>0.8863203045847622</v>
+        <v>0.8933882495973998</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.98243799226777</v>
+        <v>25.58595039381421</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08773975603041478</v>
+        <v>0.08755180728097069</v>
       </c>
       <c r="C7">
-        <v>10678.50279947336</v>
+        <v>10597.43957194958</v>
       </c>
       <c r="D7">
-        <v>10651.56279947336</v>
+        <v>10699.51157194958</v>
       </c>
       <c r="E7">
-        <v>-5205.44</v>
+        <v>-5076.428</v>
       </c>
       <c r="F7">
-        <v>645.0600000000001</v>
+        <v>774.0720000000001</v>
       </c>
       <c r="G7">
         <v>672</v>
@@ -1989,28 +1989,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M7">
-        <v>32.446518</v>
+        <v>38.9358216</v>
       </c>
       <c r="N7">
-        <v>797.7284819999999</v>
+        <v>791.2391783999998</v>
       </c>
       <c r="O7">
-        <v>199.4321205</v>
+        <v>197.8097945999999</v>
       </c>
       <c r="P7">
-        <v>598.2963614999999</v>
+        <v>593.4293837999999</v>
       </c>
       <c r="Q7">
-        <v>998.4963614999998</v>
+        <v>993.6293837999998</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09037211161096292</v>
+        <v>0.09073224178826669</v>
       </c>
       <c r="T7">
-        <v>0.8933882495973998</v>
+        <v>0.900606576418817</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.58595039381421</v>
+        <v>21.32162532817851</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08755180728097069</v>
+        <v>0.08736385853152659</v>
       </c>
       <c r="C8">
-        <v>10597.43957194958</v>
+        <v>10516.80998615891</v>
       </c>
       <c r="D8">
-        <v>10699.51157194958</v>
+        <v>10747.89398615892</v>
       </c>
       <c r="E8">
-        <v>-5076.428</v>
+        <v>-4947.416</v>
       </c>
       <c r="F8">
-        <v>774.072</v>
+        <v>903.0839999999999</v>
       </c>
       <c r="G8">
         <v>672</v>
@@ -2071,28 +2071,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M8">
-        <v>38.9358216</v>
+        <v>45.4251252</v>
       </c>
       <c r="N8">
-        <v>791.2391783999999</v>
+        <v>784.7498747999998</v>
       </c>
       <c r="O8">
-        <v>197.8097946</v>
+        <v>196.1874687</v>
       </c>
       <c r="P8">
-        <v>593.4293837999999</v>
+        <v>588.5624060999999</v>
       </c>
       <c r="Q8">
-        <v>993.6293837999998</v>
+        <v>988.7624060999998</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09073224178826669</v>
+        <v>0.09110011670056622</v>
       </c>
       <c r="T8">
-        <v>0.900606576418817</v>
+        <v>0.9079801360751033</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.32162532817851</v>
+        <v>18.27567885272444</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08736385853152658</v>
+        <v>0.08717590978208251</v>
       </c>
       <c r="C9">
-        <v>10516.80998615892</v>
+        <v>10436.61995151256</v>
       </c>
       <c r="D9">
-        <v>10747.89398615892</v>
+        <v>10796.71595151255</v>
       </c>
       <c r="E9">
-        <v>-4947.416</v>
+        <v>-4818.404</v>
       </c>
       <c r="F9">
-        <v>903.0840000000002</v>
+        <v>1032.096</v>
       </c>
       <c r="G9">
         <v>672</v>
@@ -2153,28 +2153,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M9">
-        <v>45.4251252</v>
+        <v>51.9144288</v>
       </c>
       <c r="N9">
-        <v>784.7498747999998</v>
+        <v>778.2605711999998</v>
       </c>
       <c r="O9">
-        <v>196.1874687</v>
+        <v>194.5651428</v>
       </c>
       <c r="P9">
-        <v>588.5624060999999</v>
+        <v>583.6954283999999</v>
       </c>
       <c r="Q9">
-        <v>988.7624060999998</v>
+        <v>983.8954283999998</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09110011670056622</v>
+        <v>0.09147598889356795</v>
       </c>
       <c r="T9">
-        <v>0.9079801360751033</v>
+        <v>0.9155139905065265</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.27567885272443</v>
+        <v>15.99121899613388</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08717590978208251</v>
+        <v>0.08698796103263844</v>
       </c>
       <c r="C10">
-        <v>10436.61995151256</v>
+        <v>10356.8754852849</v>
       </c>
       <c r="D10">
-        <v>10796.71595151255</v>
+        <v>10845.9834852849</v>
       </c>
       <c r="E10">
-        <v>-4818.404</v>
+        <v>-4689.392</v>
       </c>
       <c r="F10">
-        <v>1032.096</v>
+        <v>1161.108</v>
       </c>
       <c r="G10">
         <v>672</v>
@@ -2235,28 +2235,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M10">
-        <v>51.9144288</v>
+        <v>58.4037324</v>
       </c>
       <c r="N10">
-        <v>778.2605711999998</v>
+        <v>771.7712675999999</v>
       </c>
       <c r="O10">
-        <v>194.5651428</v>
+        <v>192.9428169</v>
       </c>
       <c r="P10">
-        <v>583.6954283999999</v>
+        <v>578.8284506999998</v>
       </c>
       <c r="Q10">
-        <v>983.8954283999998</v>
+        <v>979.0284506999998</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09147598889356795</v>
+        <v>0.09186012201388838</v>
       </c>
       <c r="T10">
-        <v>0.9155139905065265</v>
+        <v>0.9232134241562224</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.99121899613388</v>
+        <v>14.21441688545234</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08698796103263844</v>
+        <v>0.08680001228319432</v>
       </c>
       <c r="C11">
-        <v>10356.8754852849</v>
+        <v>10277.58271508587</v>
       </c>
       <c r="D11">
-        <v>10845.9834852849</v>
+        <v>10895.70271508587</v>
       </c>
       <c r="E11">
-        <v>-4689.392</v>
+        <v>-4560.38</v>
       </c>
       <c r="F11">
-        <v>1161.108</v>
+        <v>1290.12</v>
       </c>
       <c r="G11">
         <v>672</v>
@@ -2317,28 +2317,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M11">
-        <v>58.4037324</v>
+        <v>64.893036</v>
       </c>
       <c r="N11">
-        <v>771.7712675999999</v>
+        <v>765.2819639999998</v>
       </c>
       <c r="O11">
-        <v>192.9428169</v>
+        <v>191.3204909999999</v>
       </c>
       <c r="P11">
-        <v>578.8284506999998</v>
+        <v>573.9614729999998</v>
       </c>
       <c r="Q11">
-        <v>979.0284506999998</v>
+        <v>974.1614729999998</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09186012201388838</v>
+        <v>0.09225279142577147</v>
       </c>
       <c r="T11">
-        <v>0.9232134241562224</v>
+        <v>0.9310839563314672</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.21441688545234</v>
+        <v>12.7929751969071</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08680001228319432</v>
+        <v>0.08661206353375024</v>
       </c>
       <c r="C12">
-        <v>10277.58271508587</v>
+        <v>10198.74788140145</v>
       </c>
       <c r="D12">
-        <v>10895.70271508587</v>
+        <v>10945.87988140145</v>
       </c>
       <c r="E12">
-        <v>-4560.38</v>
+        <v>-4431.368</v>
       </c>
       <c r="F12">
-        <v>1290.12</v>
+        <v>1419.132</v>
       </c>
       <c r="G12">
         <v>672</v>
@@ -2399,28 +2399,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M12">
-        <v>64.89303600000001</v>
+        <v>71.38233959999999</v>
       </c>
       <c r="N12">
-        <v>765.2819639999998</v>
+        <v>758.7926603999998</v>
       </c>
       <c r="O12">
-        <v>191.3204909999999</v>
+        <v>189.6981651</v>
       </c>
       <c r="P12">
-        <v>573.9614729999998</v>
+        <v>569.0944952999998</v>
       </c>
       <c r="Q12">
-        <v>974.1614729999998</v>
+        <v>969.2944952999998</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09225279142577147</v>
+        <v>0.09265428486938229</v>
       </c>
       <c r="T12">
-        <v>0.9310839563314672</v>
+        <v>0.9391313543982908</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.7929751969071</v>
+        <v>11.62997745173373</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08661206353375024</v>
+        <v>0.08642411478430617</v>
       </c>
       <c r="C13">
-        <v>10198.74788140145</v>
+        <v>10120.37734020486</v>
       </c>
       <c r="D13">
-        <v>10945.87988140145</v>
+        <v>10996.52134020486</v>
       </c>
       <c r="E13">
-        <v>-4431.368</v>
+        <v>-4302.356</v>
       </c>
       <c r="F13">
-        <v>1419.132</v>
+        <v>1548.144</v>
       </c>
       <c r="G13">
         <v>672</v>
@@ -2481,28 +2481,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M13">
-        <v>71.38233959999999</v>
+        <v>77.87164319999999</v>
       </c>
       <c r="N13">
-        <v>758.7926603999998</v>
+        <v>752.3033567999998</v>
       </c>
       <c r="O13">
-        <v>189.6981651</v>
+        <v>188.0758392</v>
       </c>
       <c r="P13">
-        <v>569.0944952999998</v>
+        <v>564.2275175999998</v>
       </c>
       <c r="Q13">
-        <v>969.2944952999998</v>
+        <v>964.4275175999998</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09265428486938229</v>
+        <v>0.09306490316398427</v>
       </c>
       <c r="T13">
-        <v>0.9391313543982908</v>
+        <v>0.9473616478757237</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.62997745173373</v>
+        <v>10.66081266408925</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08642411478430617</v>
+        <v>0.08623616603486206</v>
       </c>
       <c r="C14">
-        <v>10120.37734020486</v>
+        <v>10042.4775656405</v>
       </c>
       <c r="D14">
-        <v>10996.52134020486</v>
+        <v>11047.6335656405</v>
       </c>
       <c r="E14">
-        <v>-4302.356</v>
+        <v>-4173.344</v>
       </c>
       <c r="F14">
-        <v>1548.144</v>
+        <v>1677.156</v>
       </c>
       <c r="G14">
         <v>672</v>
@@ -2563,28 +2563,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M14">
-        <v>77.87164319999999</v>
+        <v>84.36094680000001</v>
       </c>
       <c r="N14">
-        <v>752.3033567999998</v>
+        <v>745.8140531999999</v>
       </c>
       <c r="O14">
-        <v>188.0758392</v>
+        <v>186.4535133</v>
       </c>
       <c r="P14">
-        <v>564.2275175999998</v>
+        <v>559.3605398999999</v>
       </c>
       <c r="Q14">
-        <v>964.4275175999998</v>
+        <v>959.5605398999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09306490316398427</v>
+        <v>0.09348496095961156</v>
       </c>
       <c r="T14">
-        <v>0.9473616478757237</v>
+        <v>0.9557811435020632</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.66081266408925</v>
+        <v>9.840750151467004</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08623616603486206</v>
+        <v>0.08604821728541798</v>
       </c>
       <c r="C15">
-        <v>10042.4775656405</v>
+        <v>9965.055152783059</v>
       </c>
       <c r="D15">
-        <v>11047.6335656405</v>
+        <v>11099.22315278306</v>
       </c>
       <c r="E15">
-        <v>-4173.344</v>
+        <v>-4044.331999999999</v>
       </c>
       <c r="F15">
-        <v>1677.156</v>
+        <v>1806.168</v>
       </c>
       <c r="G15">
         <v>672</v>
@@ -2645,28 +2645,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M15">
-        <v>84.36094680000001</v>
+        <v>90.85025040000001</v>
       </c>
       <c r="N15">
-        <v>745.8140531999999</v>
+        <v>739.3247495999998</v>
       </c>
       <c r="O15">
-        <v>186.4535133</v>
+        <v>184.8311873999999</v>
       </c>
       <c r="P15">
-        <v>559.3605398999999</v>
+        <v>554.4935621999998</v>
       </c>
       <c r="Q15">
-        <v>959.5605398999999</v>
+        <v>954.6935621999997</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09348496095961156</v>
+        <v>0.09391478754118371</v>
       </c>
       <c r="T15">
-        <v>0.9557811435020632</v>
+        <v>0.9643964413522712</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.840750151467004</v>
+        <v>9.137839426362216</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08604821728541798</v>
+        <v>0.08602901853597389</v>
       </c>
       <c r="C16">
-        <v>9965.055152783059</v>
+        <v>9841.340105383177</v>
       </c>
       <c r="D16">
-        <v>11099.22315278306</v>
+        <v>11104.52010538318</v>
       </c>
       <c r="E16">
-        <v>-4044.331999999999</v>
+        <v>-3915.32</v>
       </c>
       <c r="F16">
-        <v>1806.168</v>
+        <v>1935.18</v>
       </c>
       <c r="G16">
         <v>672</v>
@@ -2727,45 +2727,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M16">
-        <v>90.85025040000001</v>
+        <v>100.242324</v>
       </c>
       <c r="N16">
-        <v>739.3247495999998</v>
+        <v>729.9326759999998</v>
       </c>
       <c r="O16">
-        <v>184.8311873999999</v>
+        <v>182.4831689999999</v>
       </c>
       <c r="P16">
-        <v>554.4935621999998</v>
+        <v>547.4495069999998</v>
       </c>
       <c r="Q16">
-        <v>954.6935621999997</v>
+        <v>947.6495069999997</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09391478754118371</v>
+        <v>0.09435472768938105</v>
       </c>
       <c r="T16">
-        <v>0.9643964413522712</v>
+        <v>0.9732144520930721</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.137839426362216</v>
+        <v>8.281681498126478</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08602901853597389</v>
+        <v>0.08585231978652981</v>
       </c>
       <c r="C17">
-        <v>9841.340105383177</v>
+        <v>9761.317897391622</v>
       </c>
       <c r="D17">
-        <v>11104.52010538318</v>
+        <v>11153.50989739162</v>
       </c>
       <c r="E17">
-        <v>-3915.32</v>
+        <v>-3786.308</v>
       </c>
       <c r="F17">
-        <v>1935.18</v>
+        <v>2064.192</v>
       </c>
       <c r="G17">
         <v>672</v>
@@ -2809,28 +2809,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M17">
-        <v>100.242324</v>
+        <v>106.9251456</v>
       </c>
       <c r="N17">
-        <v>729.9326759999999</v>
+        <v>723.2498543999999</v>
       </c>
       <c r="O17">
-        <v>182.483169</v>
+        <v>180.8124636</v>
       </c>
       <c r="P17">
-        <v>547.4495069999999</v>
+        <v>542.4373907999999</v>
       </c>
       <c r="Q17">
-        <v>947.6495069999999</v>
+        <v>942.6373907999998</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09435472768938105</v>
+        <v>0.09480514260301168</v>
       </c>
       <c r="T17">
-        <v>0.9732144520930721</v>
+        <v>0.9822424154705589</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.281681498126479</v>
+        <v>7.764076404493574</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08585231978652981</v>
+        <v>0.08567562103708573</v>
       </c>
       <c r="C18">
-        <v>9761.317897391622</v>
+        <v>9681.729861195179</v>
       </c>
       <c r="D18">
-        <v>11153.50989739162</v>
+        <v>11202.93386119518</v>
       </c>
       <c r="E18">
-        <v>-3786.308</v>
+        <v>-3657.296</v>
       </c>
       <c r="F18">
-        <v>2064.192</v>
+        <v>2193.204</v>
       </c>
       <c r="G18">
         <v>672</v>
@@ -2891,28 +2891,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M18">
-        <v>106.9251456</v>
+        <v>113.6079672</v>
       </c>
       <c r="N18">
-        <v>723.2498543999999</v>
+        <v>716.5670327999999</v>
       </c>
       <c r="O18">
-        <v>180.8124636</v>
+        <v>179.1417582</v>
       </c>
       <c r="P18">
-        <v>542.4373907999999</v>
+        <v>537.4252746</v>
       </c>
       <c r="Q18">
-        <v>942.6373907999998</v>
+        <v>937.6252745999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09480514260301168</v>
+        <v>0.0952664108880551</v>
       </c>
       <c r="T18">
-        <v>0.9822424154705589</v>
+        <v>0.9914879201342504</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.764076404493574</v>
+        <v>7.307366027758658</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08567562103708573</v>
+        <v>0.08549892228764162</v>
       </c>
       <c r="C19">
-        <v>9681.729861195179</v>
+        <v>9602.581794251983</v>
       </c>
       <c r="D19">
-        <v>11202.93386119518</v>
+        <v>11252.79779425198</v>
       </c>
       <c r="E19">
-        <v>-3657.296</v>
+        <v>-3528.284</v>
       </c>
       <c r="F19">
-        <v>2193.204</v>
+        <v>2322.216</v>
       </c>
       <c r="G19">
         <v>672</v>
@@ -2973,28 +2973,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M19">
-        <v>113.6079672</v>
+        <v>120.2907888</v>
       </c>
       <c r="N19">
-        <v>716.5670327999999</v>
+        <v>709.8842111999999</v>
       </c>
       <c r="O19">
-        <v>179.1417582</v>
+        <v>177.4710528</v>
       </c>
       <c r="P19">
-        <v>537.4252746</v>
+        <v>532.4131583999999</v>
       </c>
       <c r="Q19">
-        <v>937.6252745999999</v>
+        <v>932.6131583999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0952664108880551</v>
+        <v>0.09573892961907515</v>
       </c>
       <c r="T19">
-        <v>0.9914879201342504</v>
+        <v>1.00095892491169</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.307366027758658</v>
+        <v>6.901401248438732</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08549892228764162</v>
+        <v>0.08556447353819754</v>
       </c>
       <c r="C20">
-        <v>9602.581794251983</v>
+        <v>9455.019694073802</v>
       </c>
       <c r="D20">
-        <v>11252.79779425198</v>
+        <v>11234.2476940738</v>
       </c>
       <c r="E20">
-        <v>-3528.284</v>
+        <v>-3399.272</v>
       </c>
       <c r="F20">
-        <v>2322.216</v>
+        <v>2451.228</v>
       </c>
       <c r="G20">
         <v>672</v>
@@ -3055,45 +3055,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M20">
-        <v>120.2907888</v>
+        <v>131.140698</v>
       </c>
       <c r="N20">
-        <v>709.8842111999999</v>
+        <v>699.0343019999998</v>
       </c>
       <c r="O20">
-        <v>177.4710528</v>
+        <v>174.7585754999999</v>
       </c>
       <c r="P20">
-        <v>532.4131583999999</v>
+        <v>524.2757264999998</v>
       </c>
       <c r="Q20">
-        <v>932.6131583999999</v>
+        <v>924.4757264999997</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09573892961907515</v>
+        <v>0.09622311547925622</v>
       </c>
       <c r="T20">
-        <v>1.00095892491169</v>
+        <v>1.010663781658943</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.901401248438733</v>
+        <v>6.330414681794661</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08556447353819754</v>
+        <v>0.08540052478875346</v>
       </c>
       <c r="C21">
-        <v>9455.019694073802</v>
+        <v>9372.518210543312</v>
       </c>
       <c r="D21">
-        <v>11234.2476940738</v>
+        <v>11280.75821054331</v>
       </c>
       <c r="E21">
-        <v>-3399.272</v>
+        <v>-3270.26</v>
       </c>
       <c r="F21">
-        <v>2451.228</v>
+        <v>2580.24</v>
       </c>
       <c r="G21">
         <v>672</v>
@@ -3137,28 +3137,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M21">
-        <v>131.140698</v>
+        <v>138.04284</v>
       </c>
       <c r="N21">
-        <v>699.0343019999998</v>
+        <v>692.1321599999999</v>
       </c>
       <c r="O21">
-        <v>174.7585754999999</v>
+        <v>173.03304</v>
       </c>
       <c r="P21">
-        <v>524.2757264999998</v>
+        <v>519.0991199999999</v>
       </c>
       <c r="Q21">
-        <v>924.4757264999997</v>
+        <v>919.2991199999998</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09622311547925622</v>
+        <v>0.09671940598594181</v>
       </c>
       <c r="T21">
-        <v>1.010663781658943</v>
+        <v>1.020611259824878</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.330414681794661</v>
+        <v>6.013893947704928</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08540052478875346</v>
+        <v>0.08523657603930937</v>
       </c>
       <c r="C22">
-        <v>9372.518210543312</v>
+        <v>9290.403441163846</v>
       </c>
       <c r="D22">
-        <v>11280.75821054331</v>
+        <v>11327.65544116385</v>
       </c>
       <c r="E22">
-        <v>-3270.26</v>
+        <v>-3141.248</v>
       </c>
       <c r="F22">
-        <v>2580.24</v>
+        <v>2709.252</v>
       </c>
       <c r="G22">
         <v>672</v>
@@ -3219,28 +3219,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M22">
-        <v>138.04284</v>
+        <v>144.944982</v>
       </c>
       <c r="N22">
-        <v>692.1321599999999</v>
+        <v>685.2300179999999</v>
       </c>
       <c r="O22">
-        <v>173.03304</v>
+        <v>171.3075045</v>
       </c>
       <c r="P22">
-        <v>519.0991199999999</v>
+        <v>513.9225134999999</v>
       </c>
       <c r="Q22">
-        <v>919.2991199999998</v>
+        <v>914.1225134999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09671940598594181</v>
+        <v>0.09722826080925237</v>
       </c>
       <c r="T22">
-        <v>1.020611259824878</v>
+        <v>1.030810572881089</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.013893947704928</v>
+        <v>5.727518045433265</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08523657603930937</v>
+        <v>0.08520462728986528</v>
       </c>
       <c r="C23">
-        <v>9290.403441163846</v>
+        <v>9170.575754031892</v>
       </c>
       <c r="D23">
-        <v>11327.65544116385</v>
+        <v>11336.83975403189</v>
       </c>
       <c r="E23">
-        <v>-3141.248</v>
+        <v>-3012.236</v>
       </c>
       <c r="F23">
-        <v>2709.252</v>
+        <v>2838.264</v>
       </c>
       <c r="G23">
         <v>672</v>
@@ -3301,45 +3301,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M23">
-        <v>144.944982</v>
+        <v>154.1177352</v>
       </c>
       <c r="N23">
-        <v>685.2300179999999</v>
+        <v>676.0572647999999</v>
       </c>
       <c r="O23">
-        <v>171.3075045</v>
+        <v>169.0143162</v>
       </c>
       <c r="P23">
-        <v>513.9225134999999</v>
+        <v>507.0429485999999</v>
       </c>
       <c r="Q23">
-        <v>914.1225134999999</v>
+        <v>907.2429485999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09722826080925237</v>
+        <v>0.09775016319213498</v>
       </c>
       <c r="T23">
-        <v>1.030810572881089</v>
+        <v>1.041271406784895</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>5.727518045433266</v>
+        <v>5.386628598731185</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08520462728986528</v>
+        <v>0.08504667854042119</v>
       </c>
       <c r="C24">
-        <v>9170.575754031892</v>
+        <v>9087.189007642921</v>
       </c>
       <c r="D24">
-        <v>11336.83975403189</v>
+        <v>11382.46500764292</v>
       </c>
       <c r="E24">
-        <v>-3012.236</v>
+        <v>-2883.224</v>
       </c>
       <c r="F24">
-        <v>2838.264</v>
+        <v>2967.276</v>
       </c>
       <c r="G24">
         <v>672</v>
@@ -3383,28 +3383,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M24">
-        <v>154.1177352</v>
+        <v>161.1230868</v>
       </c>
       <c r="N24">
-        <v>676.0572647999999</v>
+        <v>669.0519131999998</v>
       </c>
       <c r="O24">
-        <v>169.0143162</v>
+        <v>167.2629783</v>
       </c>
       <c r="P24">
-        <v>507.0429485999999</v>
+        <v>501.7889348999998</v>
       </c>
       <c r="Q24">
-        <v>907.2429485999999</v>
+        <v>901.9889348999998</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09775016319213498</v>
+        <v>0.09828562148106648</v>
       </c>
       <c r="T24">
-        <v>1.041271406784895</v>
+        <v>1.052003950660229</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.386628598731185</v>
+        <v>5.15242735530809</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08504667854042119</v>
+        <v>0.08488872979097711</v>
       </c>
       <c r="C25">
-        <v>9087.189007642921</v>
+        <v>9004.170983992675</v>
       </c>
       <c r="D25">
-        <v>11382.46500764292</v>
+        <v>11428.45898399268</v>
       </c>
       <c r="E25">
-        <v>-2883.224</v>
+        <v>-2754.212</v>
       </c>
       <c r="F25">
-        <v>2967.276</v>
+        <v>3096.288</v>
       </c>
       <c r="G25">
         <v>672</v>
@@ -3465,28 +3465,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M25">
-        <v>161.1230868</v>
+        <v>168.1284384</v>
       </c>
       <c r="N25">
-        <v>669.0519131999998</v>
+        <v>662.0465615999998</v>
       </c>
       <c r="O25">
-        <v>167.2629783</v>
+        <v>165.5116403999999</v>
       </c>
       <c r="P25">
-        <v>501.7889348999998</v>
+        <v>496.5349211999999</v>
       </c>
       <c r="Q25">
-        <v>901.9889348999998</v>
+        <v>896.7349211999998</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09828562148106648</v>
+        <v>0.09883517077760146</v>
       </c>
       <c r="T25">
-        <v>1.052003950660229</v>
+        <v>1.063018929900704</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.15242735530809</v>
+        <v>4.937742882170252</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08488872979097711</v>
+        <v>0.08473078104153302</v>
       </c>
       <c r="C26">
-        <v>9004.170983992675</v>
+        <v>8921.526170992314</v>
       </c>
       <c r="D26">
-        <v>11428.45898399268</v>
+        <v>11474.82617099232</v>
       </c>
       <c r="E26">
-        <v>-2754.212</v>
+        <v>-2625.2</v>
       </c>
       <c r="F26">
-        <v>3096.288</v>
+        <v>3225.3</v>
       </c>
       <c r="G26">
         <v>672</v>
@@ -3547,28 +3547,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M26">
-        <v>168.1284384</v>
+        <v>175.13379</v>
       </c>
       <c r="N26">
-        <v>662.0465615999999</v>
+        <v>655.0412099999999</v>
       </c>
       <c r="O26">
-        <v>165.5116404</v>
+        <v>163.7603025</v>
       </c>
       <c r="P26">
-        <v>496.5349211999999</v>
+        <v>491.2809074999999</v>
       </c>
       <c r="Q26">
-        <v>896.7349211999999</v>
+        <v>891.4809074999998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09883517077760146</v>
+        <v>0.09939937472204402</v>
       </c>
       <c r="T26">
-        <v>1.063018929900704</v>
+        <v>1.074327641920924</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.937742882170253</v>
+        <v>4.740233166883443</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08473078104153302</v>
+        <v>0.08457283229208894</v>
       </c>
       <c r="C27">
-        <v>8921.526170992314</v>
+        <v>8839.259129682534</v>
       </c>
       <c r="D27">
-        <v>11474.82617099232</v>
+        <v>11521.57112968253</v>
       </c>
       <c r="E27">
-        <v>-2625.2</v>
+        <v>-2496.188</v>
       </c>
       <c r="F27">
-        <v>3225.3</v>
+        <v>3354.312</v>
       </c>
       <c r="G27">
         <v>672</v>
@@ -3629,28 +3629,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M27">
-        <v>175.13379</v>
+        <v>182.1391416</v>
       </c>
       <c r="N27">
-        <v>655.0412099999999</v>
+        <v>648.0358583999998</v>
       </c>
       <c r="O27">
-        <v>163.7603025</v>
+        <v>162.0089646</v>
       </c>
       <c r="P27">
-        <v>491.2809074999999</v>
+        <v>486.0268937999999</v>
       </c>
       <c r="Q27">
-        <v>891.4809074999998</v>
+        <v>886.2268937999997</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09939937472204402</v>
+        <v>0.0999788274217418</v>
       </c>
       <c r="T27">
-        <v>1.074327641920924</v>
+        <v>1.085941994806556</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.740233166883443</v>
+        <v>4.557916506618694</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08457283229208894</v>
+        <v>0.08441488354264483</v>
       </c>
       <c r="C28">
-        <v>8839.259129682534</v>
+        <v>8757.374495729227</v>
       </c>
       <c r="D28">
-        <v>11521.57112968253</v>
+        <v>11568.69849572923</v>
       </c>
       <c r="E28">
-        <v>-2496.188</v>
+        <v>-2367.175999999999</v>
       </c>
       <c r="F28">
-        <v>3354.312</v>
+        <v>3483.324000000001</v>
       </c>
       <c r="G28">
         <v>672</v>
@@ -3711,28 +3711,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M28">
-        <v>182.1391416</v>
+        <v>189.1444932</v>
       </c>
       <c r="N28">
-        <v>648.0358583999998</v>
+        <v>641.0305067999998</v>
       </c>
       <c r="O28">
-        <v>162.0089646</v>
+        <v>160.2576266999999</v>
       </c>
       <c r="P28">
-        <v>486.0268937999999</v>
+        <v>480.7728800999998</v>
       </c>
       <c r="Q28">
-        <v>886.2268937999997</v>
+        <v>880.9728800999998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0999788274217418</v>
+        <v>0.1005741555378696</v>
       </c>
       <c r="T28">
-        <v>1.085941994806556</v>
+        <v>1.097874549141109</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.557916506618694</v>
+        <v>4.389104784151336</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08441488354264483</v>
+        <v>0.08446693479320075</v>
       </c>
       <c r="C29">
-        <v>8757.374495729227</v>
+        <v>8612.789365166185</v>
       </c>
       <c r="D29">
-        <v>11568.69849572923</v>
+        <v>11553.12536516619</v>
       </c>
       <c r="E29">
-        <v>-2367.175999999999</v>
+        <v>-2238.163999999999</v>
       </c>
       <c r="F29">
-        <v>3483.324000000001</v>
+        <v>3612.336000000001</v>
       </c>
       <c r="G29">
         <v>672</v>
@@ -3793,45 +3793,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M29">
-        <v>189.1444932</v>
+        <v>199.7621808</v>
       </c>
       <c r="N29">
-        <v>641.0305067999998</v>
+        <v>630.4128191999998</v>
       </c>
       <c r="O29">
-        <v>160.2576266999999</v>
+        <v>157.6032048</v>
       </c>
       <c r="P29">
-        <v>480.7728800999998</v>
+        <v>472.8096143999999</v>
       </c>
       <c r="Q29">
-        <v>880.9728800999998</v>
+        <v>873.0096143999998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1005741555378696</v>
+        <v>0.1011860205461122</v>
       </c>
       <c r="T29">
-        <v>1.097874549141109</v>
+        <v>1.110138563318288</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.389104784151336</v>
+        <v>4.155816664973051</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08446693479320075</v>
+        <v>0.08431648604375666</v>
       </c>
       <c r="C30">
-        <v>8612.789365166185</v>
+        <v>8528.90487917111</v>
       </c>
       <c r="D30">
-        <v>11553.12536516619</v>
+        <v>11598.25287917111</v>
       </c>
       <c r="E30">
-        <v>-2238.163999999999</v>
+        <v>-2109.151999999999</v>
       </c>
       <c r="F30">
-        <v>3612.336000000001</v>
+        <v>3741.348000000001</v>
       </c>
       <c r="G30">
         <v>672</v>
@@ -3875,28 +3875,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M30">
-        <v>199.7621808</v>
+        <v>206.8965444000001</v>
       </c>
       <c r="N30">
-        <v>630.4128191999998</v>
+        <v>623.2784555999998</v>
       </c>
       <c r="O30">
-        <v>157.6032048</v>
+        <v>155.8196139</v>
       </c>
       <c r="P30">
-        <v>472.8096143999999</v>
+        <v>467.4588416999999</v>
       </c>
       <c r="Q30">
-        <v>873.0096143999998</v>
+        <v>867.6588416999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1011860205461122</v>
+        <v>0.1018151211883897</v>
       </c>
       <c r="T30">
-        <v>1.110138563318288</v>
+        <v>1.122748042683557</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.155816664973051</v>
+        <v>4.012512642042946</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08431648604375666</v>
+        <v>0.08416603729431255</v>
       </c>
       <c r="C31">
-        <v>8528.90487917111</v>
+        <v>8445.374319644674</v>
       </c>
       <c r="D31">
-        <v>11598.25287917111</v>
+        <v>11643.73431964467</v>
       </c>
       <c r="E31">
-        <v>-2109.152</v>
+        <v>-1980.14</v>
       </c>
       <c r="F31">
-        <v>3741.348</v>
+        <v>3870.36</v>
       </c>
       <c r="G31">
         <v>672</v>
@@ -3957,28 +3957,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M31">
-        <v>206.8965444</v>
+        <v>214.030908</v>
       </c>
       <c r="N31">
-        <v>623.2784555999998</v>
+        <v>616.1440919999998</v>
       </c>
       <c r="O31">
-        <v>155.8196139</v>
+        <v>154.0360229999999</v>
       </c>
       <c r="P31">
-        <v>467.4588416999999</v>
+        <v>462.1080689999998</v>
       </c>
       <c r="Q31">
-        <v>867.6588416999998</v>
+        <v>862.3080689999997</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1018151211883897</v>
+        <v>0.1024621961347322</v>
       </c>
       <c r="T31">
-        <v>1.122748042683557</v>
+        <v>1.135717792887834</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.012512642042946</v>
+        <v>3.878762220641515</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08416603729431255</v>
+        <v>0.08401558854486849</v>
       </c>
       <c r="C32">
-        <v>8445.374319644674</v>
+        <v>8362.201866645049</v>
       </c>
       <c r="D32">
-        <v>11643.73431964467</v>
+        <v>11689.57386664505</v>
       </c>
       <c r="E32">
-        <v>-1980.14</v>
+        <v>-1851.128</v>
       </c>
       <c r="F32">
-        <v>3870.36</v>
+        <v>3999.372</v>
       </c>
       <c r="G32">
         <v>672</v>
@@ -4039,28 +4039,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M32">
-        <v>214.030908</v>
+        <v>221.1652716</v>
       </c>
       <c r="N32">
-        <v>616.1440919999998</v>
+        <v>609.0097283999999</v>
       </c>
       <c r="O32">
-        <v>154.0360229999999</v>
+        <v>152.2524321</v>
       </c>
       <c r="P32">
-        <v>462.1080689999998</v>
+        <v>456.7572962999999</v>
       </c>
       <c r="Q32">
-        <v>862.3080689999997</v>
+        <v>856.9572962999998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1024621961347322</v>
+        <v>0.103128026876621</v>
       </c>
       <c r="T32">
-        <v>1.135717792887834</v>
+        <v>1.14906347788064</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.878762220641515</v>
+        <v>3.753640858685337</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08401558854486849</v>
+        <v>0.0838651397954244</v>
       </c>
       <c r="C33">
-        <v>8362.201866645049</v>
+        <v>8279.39176631553</v>
       </c>
       <c r="D33">
-        <v>11689.57386664505</v>
+        <v>11735.77576631553</v>
       </c>
       <c r="E33">
-        <v>-1851.128</v>
+        <v>-1722.116</v>
       </c>
       <c r="F33">
-        <v>3999.372</v>
+        <v>4128.384</v>
       </c>
       <c r="G33">
         <v>672</v>
@@ -4121,28 +4121,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M33">
-        <v>221.1652716</v>
+        <v>228.2996352</v>
       </c>
       <c r="N33">
-        <v>609.0097283999999</v>
+        <v>601.8753647999998</v>
       </c>
       <c r="O33">
-        <v>152.2524321</v>
+        <v>150.4688412</v>
       </c>
       <c r="P33">
-        <v>456.7572962999999</v>
+        <v>451.4065235999999</v>
       </c>
       <c r="Q33">
-        <v>856.9572962999998</v>
+        <v>851.6065235999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.103128026876621</v>
+        <v>0.1038134408756241</v>
       </c>
       <c r="T33">
-        <v>1.14906347788064</v>
+        <v>1.162801683020294</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.753640858685337</v>
+        <v>3.63633958185142</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0838651397954244</v>
+        <v>0.0837146910459803</v>
       </c>
       <c r="C34">
-        <v>8279.39176631553</v>
+        <v>8196.948332195634</v>
       </c>
       <c r="D34">
-        <v>11735.77576631553</v>
+        <v>11782.34433219563</v>
       </c>
       <c r="E34">
-        <v>-1722.116</v>
+        <v>-1593.103999999999</v>
       </c>
       <c r="F34">
-        <v>4128.384</v>
+        <v>4257.396000000001</v>
       </c>
       <c r="G34">
         <v>672</v>
@@ -4203,28 +4203,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M34">
-        <v>228.2996352</v>
+        <v>235.4339988</v>
       </c>
       <c r="N34">
-        <v>601.8753647999998</v>
+        <v>594.7410011999998</v>
       </c>
       <c r="O34">
-        <v>150.4688412</v>
+        <v>148.6852503</v>
       </c>
       <c r="P34">
-        <v>451.4065235999999</v>
+        <v>446.0557508999999</v>
       </c>
       <c r="Q34">
-        <v>851.6065235999998</v>
+        <v>846.2557508999998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1038134408756241</v>
+        <v>0.1045193149940005</v>
       </c>
       <c r="T34">
-        <v>1.162801683020294</v>
+        <v>1.176949983835758</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.63633958185142</v>
+        <v>3.526147473310468</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0837146910459803</v>
+        <v>0.08356424229653621</v>
       </c>
       <c r="C35">
-        <v>8196.948332195634</v>
+        <v>8114.875946563619</v>
       </c>
       <c r="D35">
-        <v>11782.34433219563</v>
+        <v>11829.28394656362</v>
       </c>
       <c r="E35">
-        <v>-1593.103999999999</v>
+        <v>-1464.092</v>
       </c>
       <c r="F35">
-        <v>4257.396000000001</v>
+        <v>4386.408</v>
       </c>
       <c r="G35">
         <v>672</v>
@@ -4285,28 +4285,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M35">
-        <v>235.4339988</v>
+        <v>242.5683624</v>
       </c>
       <c r="N35">
-        <v>594.7410011999998</v>
+        <v>587.6066375999998</v>
       </c>
       <c r="O35">
-        <v>148.6852503</v>
+        <v>146.9016593999999</v>
       </c>
       <c r="P35">
-        <v>446.0557508999999</v>
+        <v>440.7049781999998</v>
       </c>
       <c r="Q35">
-        <v>846.2557508999998</v>
+        <v>840.9049781999997</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1045193149940005</v>
+        <v>0.1052465792371761</v>
       </c>
       <c r="T35">
-        <v>1.176949983835758</v>
+        <v>1.19152702103957</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.526147473310468</v>
+        <v>3.422437253507219</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08356424229653621</v>
+        <v>0.08341379354709214</v>
       </c>
       <c r="C36">
-        <v>8114.875946563619</v>
+        <v>8033.179061811198</v>
       </c>
       <c r="D36">
-        <v>11829.28394656362</v>
+        <v>11876.5990618112</v>
       </c>
       <c r="E36">
-        <v>-1464.092</v>
+        <v>-1335.079999999999</v>
       </c>
       <c r="F36">
-        <v>4386.408</v>
+        <v>4515.420000000001</v>
       </c>
       <c r="G36">
         <v>672</v>
@@ -4367,28 +4367,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M36">
-        <v>242.5683624</v>
+        <v>249.7027260000001</v>
       </c>
       <c r="N36">
-        <v>587.6066375999998</v>
+        <v>580.4722739999997</v>
       </c>
       <c r="O36">
-        <v>146.9016593999999</v>
+        <v>145.1180684999999</v>
       </c>
       <c r="P36">
-        <v>440.7049781999998</v>
+        <v>435.3542054999998</v>
       </c>
       <c r="Q36">
-        <v>840.9049781999997</v>
+        <v>835.5542054999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1052465792371761</v>
+        <v>0.1059962208416802</v>
       </c>
       <c r="T36">
-        <v>1.19152702103957</v>
+        <v>1.206552582465038</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.422437253507219</v>
+        <v>3.32465333197844</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08341379354709214</v>
+        <v>0.08326334479764803</v>
       </c>
       <c r="C37">
-        <v>8033.179061811198</v>
+        <v>7951.862201851407</v>
       </c>
       <c r="D37">
-        <v>11876.5990618112</v>
+        <v>11924.29420185141</v>
       </c>
       <c r="E37">
-        <v>-1335.079999999999</v>
+        <v>-1206.067999999999</v>
       </c>
       <c r="F37">
-        <v>4515.420000000001</v>
+        <v>4644.432000000001</v>
       </c>
       <c r="G37">
         <v>672</v>
@@ -4449,28 +4449,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M37">
-        <v>249.7027260000001</v>
+        <v>256.8370896000001</v>
       </c>
       <c r="N37">
-        <v>580.4722739999997</v>
+        <v>573.3379103999998</v>
       </c>
       <c r="O37">
-        <v>145.1180684999999</v>
+        <v>143.3344776</v>
       </c>
       <c r="P37">
-        <v>435.3542054999998</v>
+        <v>430.0034327999999</v>
       </c>
       <c r="Q37">
-        <v>835.5542054999997</v>
+        <v>830.2034327999997</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1059962208416802</v>
+        <v>0.1067692887463251</v>
       </c>
       <c r="T37">
-        <v>1.206552582465038</v>
+        <v>1.222047692685051</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.32465333197844</v>
+        <v>3.232301850534595</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08326334479764803</v>
+        <v>0.08311289604820396</v>
       </c>
       <c r="C38">
-        <v>7951.862201851408</v>
+        <v>7870.929963560445</v>
       </c>
       <c r="D38">
-        <v>11924.29420185141</v>
+        <v>11972.37396356045</v>
       </c>
       <c r="E38">
-        <v>-1206.068</v>
+        <v>-1077.056</v>
       </c>
       <c r="F38">
-        <v>4644.432</v>
+        <v>4773.444</v>
       </c>
       <c r="G38">
         <v>672</v>
@@ -4531,28 +4531,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M38">
-        <v>256.8370896</v>
+        <v>263.9714532</v>
       </c>
       <c r="N38">
-        <v>573.3379103999998</v>
+        <v>566.2035467999998</v>
       </c>
       <c r="O38">
-        <v>143.3344776</v>
+        <v>141.5508866999999</v>
       </c>
       <c r="P38">
-        <v>430.0034327999999</v>
+        <v>424.6526600999998</v>
       </c>
       <c r="Q38">
-        <v>830.2034327999997</v>
+        <v>824.8526600999998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1067692887463251</v>
+        <v>0.1075668984892126</v>
       </c>
       <c r="T38">
-        <v>1.222047692685051</v>
+        <v>1.238034711166017</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.232301850534596</v>
+        <v>3.144942341060688</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08311289604820396</v>
+        <v>0.08296244729875986</v>
       </c>
       <c r="C39">
-        <v>7870.929963560445</v>
+        <v>7790.387018254671</v>
       </c>
       <c r="D39">
-        <v>11972.37396356045</v>
+        <v>12020.84301825467</v>
       </c>
       <c r="E39">
-        <v>-1077.056</v>
+        <v>-948.0439999999999</v>
       </c>
       <c r="F39">
-        <v>4773.444</v>
+        <v>4902.456</v>
       </c>
       <c r="G39">
         <v>672</v>
@@ -4613,28 +4613,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M39">
-        <v>263.9714532</v>
+        <v>271.1058168</v>
       </c>
       <c r="N39">
-        <v>566.2035467999998</v>
+        <v>559.0691831999998</v>
       </c>
       <c r="O39">
-        <v>141.5508866999999</v>
+        <v>139.7672957999999</v>
       </c>
       <c r="P39">
-        <v>424.6526600999998</v>
+        <v>419.3018873999998</v>
       </c>
       <c r="Q39">
-        <v>824.8526600999998</v>
+        <v>819.5018873999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1075668984892126</v>
+        <v>0.1083902375786449</v>
       </c>
       <c r="T39">
-        <v>1.238034711166017</v>
+        <v>1.254537439920563</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.144942341060688</v>
+        <v>3.062180700506459</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08296244729875986</v>
+        <v>0.08354324854931579</v>
       </c>
       <c r="C40">
-        <v>7790.387018254671</v>
+        <v>7476.395692783613</v>
       </c>
       <c r="D40">
-        <v>12020.84301825467</v>
+        <v>11835.86369278361</v>
       </c>
       <c r="E40">
-        <v>-948.0439999999999</v>
+        <v>-819.0319999999992</v>
       </c>
       <c r="F40">
-        <v>4902.456</v>
+        <v>5031.468000000001</v>
       </c>
       <c r="G40">
         <v>672</v>
@@ -4695,45 +4695,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M40">
-        <v>271.1058168</v>
+        <v>290.8188504000001</v>
       </c>
       <c r="N40">
-        <v>559.0691831999998</v>
+        <v>539.3561495999998</v>
       </c>
       <c r="O40">
-        <v>139.7672957999999</v>
+        <v>134.8390373999999</v>
       </c>
       <c r="P40">
-        <v>419.3018873999998</v>
+        <v>404.5171121999998</v>
       </c>
       <c r="Q40">
-        <v>819.5018873999998</v>
+        <v>804.7171121999997</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1083902375786449</v>
+        <v>0.109240571392321</v>
       </c>
       <c r="T40">
-        <v>1.254537439920563</v>
+        <v>1.271581241749028</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.062180700506459</v>
+        <v>2.854612068159113</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08354324854931579</v>
+        <v>0.0834115497998717</v>
       </c>
       <c r="C41">
-        <v>7476.395692783613</v>
+        <v>7388.827569869892</v>
       </c>
       <c r="D41">
-        <v>11835.86369278361</v>
+        <v>11877.30756986989</v>
       </c>
       <c r="E41">
-        <v>-819.0319999999992</v>
+        <v>-690.0199999999995</v>
       </c>
       <c r="F41">
-        <v>5031.468000000001</v>
+        <v>5160.48</v>
       </c>
       <c r="G41">
         <v>672</v>
@@ -4777,28 +4777,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M41">
-        <v>290.8188504000001</v>
+        <v>298.275744</v>
       </c>
       <c r="N41">
-        <v>539.3561495999998</v>
+        <v>531.8992559999998</v>
       </c>
       <c r="O41">
-        <v>134.8390373999999</v>
+        <v>132.974814</v>
       </c>
       <c r="P41">
-        <v>404.5171121999998</v>
+        <v>398.9244419999999</v>
       </c>
       <c r="Q41">
-        <v>804.7171121999997</v>
+        <v>799.1244419999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.109240571392321</v>
+        <v>0.1101192496664528</v>
       </c>
       <c r="T41">
-        <v>1.271581241749028</v>
+        <v>1.289193170305109</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.854612068159113</v>
+        <v>2.783246766455135</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0834115497998717</v>
+        <v>0.08327985105042759</v>
       </c>
       <c r="C42">
-        <v>7388.827569869892</v>
+        <v>7301.550702477815</v>
       </c>
       <c r="D42">
-        <v>11877.30756986989</v>
+        <v>11919.04270247782</v>
       </c>
       <c r="E42">
-        <v>-690.0199999999995</v>
+        <v>-561.0079999999989</v>
       </c>
       <c r="F42">
-        <v>5160.48</v>
+        <v>5289.492000000001</v>
       </c>
       <c r="G42">
         <v>672</v>
@@ -4859,28 +4859,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M42">
-        <v>298.275744</v>
+        <v>305.7326376000001</v>
       </c>
       <c r="N42">
-        <v>531.8992559999998</v>
+        <v>524.4423623999998</v>
       </c>
       <c r="O42">
-        <v>132.974814</v>
+        <v>131.1105905999999</v>
       </c>
       <c r="P42">
-        <v>398.9244419999999</v>
+        <v>393.3317717999998</v>
       </c>
       <c r="Q42">
-        <v>799.1244419999998</v>
+        <v>793.5317717999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1101192496664528</v>
+        <v>0.1110277136447926</v>
       </c>
       <c r="T42">
-        <v>1.289193170305109</v>
+        <v>1.307402113388514</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.783246766455135</v>
+        <v>2.715362698980619</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08327985105042759</v>
+        <v>0.08314815230098352</v>
       </c>
       <c r="C43">
-        <v>7301.550702477815</v>
+        <v>7214.568171722683</v>
       </c>
       <c r="D43">
-        <v>11919.04270247782</v>
+        <v>11961.07217172268</v>
       </c>
       <c r="E43">
-        <v>-561.0079999999989</v>
+        <v>-431.9959999999992</v>
       </c>
       <c r="F43">
-        <v>5289.492000000001</v>
+        <v>5418.504000000001</v>
       </c>
       <c r="G43">
         <v>672</v>
@@ -4941,28 +4941,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M43">
-        <v>305.7326376000001</v>
+        <v>313.1895312000001</v>
       </c>
       <c r="N43">
-        <v>524.4423623999998</v>
+        <v>516.9854687999998</v>
       </c>
       <c r="O43">
-        <v>131.1105905999999</v>
+        <v>129.2463672</v>
       </c>
       <c r="P43">
-        <v>393.3317717999998</v>
+        <v>387.7391015999999</v>
       </c>
       <c r="Q43">
-        <v>793.5317717999998</v>
+        <v>787.9391015999997</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1110277136447926</v>
+        <v>0.111967503967213</v>
       </c>
       <c r="T43">
-        <v>1.307402113388514</v>
+        <v>1.326238951061003</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.715362698980619</v>
+        <v>2.650711206147748</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08314815230098353</v>
+        <v>0.08301645355153944</v>
       </c>
       <c r="C44">
-        <v>7214.568171722681</v>
+        <v>7127.883102332683</v>
       </c>
       <c r="D44">
-        <v>11961.07217172268</v>
+        <v>12003.39910233268</v>
       </c>
       <c r="E44">
-        <v>-431.9960000000001</v>
+        <v>-302.9839999999995</v>
       </c>
       <c r="F44">
-        <v>5418.504</v>
+        <v>5547.516000000001</v>
       </c>
       <c r="G44">
         <v>672</v>
@@ -5023,28 +5023,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M44">
-        <v>313.1895312</v>
+        <v>320.6464248</v>
       </c>
       <c r="N44">
-        <v>516.9854687999998</v>
+        <v>509.5285751999998</v>
       </c>
       <c r="O44">
-        <v>129.2463672</v>
+        <v>127.3821438</v>
       </c>
       <c r="P44">
-        <v>387.7391015999999</v>
+        <v>382.1464313999999</v>
       </c>
       <c r="Q44">
-        <v>787.9391015999997</v>
+        <v>782.3464313999998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.111967503967213</v>
+        <v>0.1129402693886657</v>
       </c>
       <c r="T44">
-        <v>1.326238951061003</v>
+        <v>1.34573673040621</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.650711206147748</v>
+        <v>2.589066759493149</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08301645355153944</v>
+        <v>0.08288475480209534</v>
       </c>
       <c r="C45">
-        <v>7127.883102332683</v>
+        <v>7041.498663423268</v>
       </c>
       <c r="D45">
-        <v>12003.39910233268</v>
+        <v>12046.02666342327</v>
       </c>
       <c r="E45">
-        <v>-302.9839999999995</v>
+        <v>-173.9719999999998</v>
       </c>
       <c r="F45">
-        <v>5547.516000000001</v>
+        <v>5676.528</v>
       </c>
       <c r="G45">
         <v>672</v>
@@ -5105,28 +5105,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M45">
-        <v>320.6464248</v>
+        <v>328.1033184</v>
       </c>
       <c r="N45">
-        <v>509.5285751999998</v>
+        <v>502.0716815999998</v>
       </c>
       <c r="O45">
-        <v>127.3821438</v>
+        <v>125.5179204</v>
       </c>
       <c r="P45">
-        <v>382.1464313999999</v>
+        <v>376.5537611999998</v>
       </c>
       <c r="Q45">
-        <v>782.3464313999998</v>
+        <v>776.7537611999998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1129402693886657</v>
+        <v>0.1139477764323131</v>
       </c>
       <c r="T45">
-        <v>1.34573673040621</v>
+        <v>1.365930859013746</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.589066759493149</v>
+        <v>2.530224333141032</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08288475480209534</v>
+        <v>0.08393430605265126</v>
       </c>
       <c r="C46">
-        <v>7041.498663423268</v>
+        <v>6580.94995389537</v>
       </c>
       <c r="D46">
-        <v>12046.02666342327</v>
+        <v>11714.48995389537</v>
       </c>
       <c r="E46">
-        <v>-173.9719999999998</v>
+        <v>-44.95999999999913</v>
       </c>
       <c r="F46">
-        <v>5676.528</v>
+        <v>5805.540000000001</v>
       </c>
       <c r="G46">
         <v>672</v>
@@ -5187,45 +5187,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M46">
-        <v>328.1033184</v>
+        <v>355.879602</v>
       </c>
       <c r="N46">
-        <v>502.0716815999998</v>
+        <v>474.2953979999998</v>
       </c>
       <c r="O46">
-        <v>125.5179204</v>
+        <v>118.5738495</v>
       </c>
       <c r="P46">
-        <v>376.5537611999998</v>
+        <v>355.7215484999999</v>
       </c>
       <c r="Q46">
-        <v>776.7537611999998</v>
+        <v>755.9215484999997</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1139477764323131</v>
+        <v>0.1149919200957295</v>
       </c>
       <c r="T46">
-        <v>1.365930859013746</v>
+        <v>1.386859319570647</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.530224333141032</v>
+        <v>2.332741172392341</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08393430605265126</v>
+        <v>0.08382885730320716</v>
       </c>
       <c r="C47">
-        <v>6580.94995389537</v>
+        <v>6484.420610583281</v>
       </c>
       <c r="D47">
-        <v>11714.48995389537</v>
+        <v>11746.97261058328</v>
       </c>
       <c r="E47">
-        <v>-44.95999999999913</v>
+        <v>84.05200000000059</v>
       </c>
       <c r="F47">
-        <v>5805.540000000001</v>
+        <v>5934.552000000001</v>
       </c>
       <c r="G47">
         <v>672</v>
@@ -5269,28 +5269,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M47">
-        <v>355.879602</v>
+        <v>363.7880376000001</v>
       </c>
       <c r="N47">
-        <v>474.2953979999998</v>
+        <v>466.3869623999998</v>
       </c>
       <c r="O47">
-        <v>118.5738495</v>
+        <v>116.5967405999999</v>
       </c>
       <c r="P47">
-        <v>355.7215484999999</v>
+        <v>349.7902217999998</v>
       </c>
       <c r="Q47">
-        <v>755.9215484999997</v>
+        <v>749.9902217999997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1149919200957295</v>
+        <v>0.1160747357466799</v>
       </c>
       <c r="T47">
-        <v>1.386859319570647</v>
+        <v>1.408562908296322</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.332741172392341</v>
+        <v>2.282029407775116</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08382885730320716</v>
+        <v>0.08471040855376308</v>
       </c>
       <c r="C48">
-        <v>6484.420610583281</v>
+        <v>6089.270094437985</v>
       </c>
       <c r="D48">
-        <v>11746.97261058328</v>
+        <v>11480.83409443799</v>
       </c>
       <c r="E48">
-        <v>84.05200000000059</v>
+        <v>213.0640000000003</v>
       </c>
       <c r="F48">
-        <v>5934.552000000001</v>
+        <v>6063.564</v>
       </c>
       <c r="G48">
         <v>672</v>
@@ -5351,45 +5351,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M48">
-        <v>363.7880376000001</v>
+        <v>388.6744524000001</v>
       </c>
       <c r="N48">
-        <v>466.3869623999998</v>
+        <v>441.5005475999998</v>
       </c>
       <c r="O48">
-        <v>116.5967405999999</v>
+        <v>110.3751368999999</v>
       </c>
       <c r="P48">
-        <v>349.7902217999998</v>
+        <v>331.1254106999999</v>
       </c>
       <c r="Q48">
-        <v>749.9902217999997</v>
+        <v>731.3254106999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1160747357466799</v>
+        <v>0.1171984123655907</v>
       </c>
       <c r="T48">
-        <v>1.408562908296322</v>
+        <v>1.431085500370136</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.282029407775116</v>
+        <v>2.135913474306859</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08471040855376308</v>
+        <v>0.084625959804319</v>
       </c>
       <c r="C49">
-        <v>6089.270094437985</v>
+        <v>5985.229584820621</v>
       </c>
       <c r="D49">
-        <v>11480.83409443799</v>
+        <v>11505.80558482062</v>
       </c>
       <c r="E49">
-        <v>213.0640000000003</v>
+        <v>342.0760000000009</v>
       </c>
       <c r="F49">
-        <v>6063.564</v>
+        <v>6192.576000000001</v>
       </c>
       <c r="G49">
         <v>672</v>
@@ -5433,28 +5433,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M49">
-        <v>388.6744524000001</v>
+        <v>396.9441216000001</v>
       </c>
       <c r="N49">
-        <v>441.5005475999998</v>
+        <v>433.2308783999998</v>
       </c>
       <c r="O49">
-        <v>110.3751368999999</v>
+        <v>108.3077195999999</v>
       </c>
       <c r="P49">
-        <v>331.1254106999999</v>
+        <v>324.9231587999998</v>
       </c>
       <c r="Q49">
-        <v>731.3254106999998</v>
+        <v>725.1231587999998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1171984123655907</v>
+        <v>0.1183653073159981</v>
       </c>
       <c r="T49">
-        <v>1.431085500370136</v>
+        <v>1.454474345985251</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.135913474306859</v>
+        <v>2.091415276925466</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.084625959804319</v>
+        <v>0.0845415110548749</v>
       </c>
       <c r="C50">
-        <v>5985.229584820622</v>
+        <v>5881.29794091744</v>
       </c>
       <c r="D50">
-        <v>11505.80558482062</v>
+        <v>11530.88594091744</v>
       </c>
       <c r="E50">
-        <v>342.076</v>
+        <v>471.0880000000006</v>
       </c>
       <c r="F50">
-        <v>6192.576</v>
+        <v>6321.588000000001</v>
       </c>
       <c r="G50">
         <v>672</v>
@@ -5515,28 +5515,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M50">
-        <v>396.9441216</v>
+        <v>405.2137908000001</v>
       </c>
       <c r="N50">
-        <v>433.2308783999998</v>
+        <v>424.9612091999998</v>
       </c>
       <c r="O50">
-        <v>108.3077196</v>
+        <v>106.2403022999999</v>
       </c>
       <c r="P50">
-        <v>324.9231587999999</v>
+        <v>318.7209068999998</v>
       </c>
       <c r="Q50">
-        <v>725.1231587999998</v>
+        <v>718.9209068999997</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1183653073159981</v>
+        <v>0.1195779628526959</v>
       </c>
       <c r="T50">
-        <v>1.454474345985251</v>
+        <v>1.47878040123233</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.091415276925466</v>
+        <v>2.048733332498415</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0845415110548749</v>
+        <v>0.08445706230543082</v>
       </c>
       <c r="C51">
-        <v>5881.29794091744</v>
+        <v>5777.475876200133</v>
       </c>
       <c r="D51">
-        <v>11530.88594091744</v>
+        <v>11556.07587620013</v>
       </c>
       <c r="E51">
-        <v>471.0880000000006</v>
+        <v>600.1000000000004</v>
       </c>
       <c r="F51">
-        <v>6321.588000000001</v>
+        <v>6450.6</v>
       </c>
       <c r="G51">
         <v>672</v>
@@ -5597,28 +5597,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M51">
-        <v>405.2137908000001</v>
+        <v>413.48346</v>
       </c>
       <c r="N51">
-        <v>424.9612091999998</v>
+        <v>416.6915399999998</v>
       </c>
       <c r="O51">
-        <v>106.2403022999999</v>
+        <v>104.172885</v>
       </c>
       <c r="P51">
-        <v>318.7209068999998</v>
+        <v>312.5186549999999</v>
       </c>
       <c r="Q51">
-        <v>718.9209068999997</v>
+        <v>712.7186549999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1195779628526959</v>
+        <v>0.1208391246108616</v>
       </c>
       <c r="T51">
-        <v>1.47878040123233</v>
+        <v>1.504058698689293</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.048733332498415</v>
+        <v>2.007758665848447</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08445706230543082</v>
+        <v>0.08735611355598673</v>
       </c>
       <c r="C52">
-        <v>5777.475876200133</v>
+        <v>4842.285113229874</v>
       </c>
       <c r="D52">
-        <v>11556.07587620013</v>
+        <v>10749.89711322987</v>
       </c>
       <c r="E52">
-        <v>600.1000000000004</v>
+        <v>729.1120000000001</v>
       </c>
       <c r="F52">
-        <v>6450.6</v>
+        <v>6579.612</v>
       </c>
       <c r="G52">
         <v>672</v>
@@ -5679,45 +5679,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M52">
-        <v>413.48346</v>
+        <v>473.0741028</v>
       </c>
       <c r="N52">
-        <v>416.6915399999998</v>
+        <v>357.1008971999998</v>
       </c>
       <c r="O52">
-        <v>104.172885</v>
+        <v>89.27522429999995</v>
       </c>
       <c r="P52">
-        <v>312.5186549999999</v>
+        <v>267.8256728999999</v>
       </c>
       <c r="Q52">
-        <v>712.7186549999998</v>
+        <v>668.0256728999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1208391246108616</v>
+        <v>0.1221517623591566</v>
       </c>
       <c r="T52">
-        <v>1.504058698689293</v>
+        <v>1.530368763389398</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.007758665848447</v>
+        <v>1.754851925071388</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08735611355598673</v>
+        <v>0.08885116480654263</v>
       </c>
       <c r="C53">
-        <v>4842.285113229874</v>
+        <v>4339.958077627417</v>
       </c>
       <c r="D53">
-        <v>10749.89711322987</v>
+        <v>10376.58207762742</v>
       </c>
       <c r="E53">
-        <v>729.1120000000001</v>
+        <v>858.1240000000007</v>
       </c>
       <c r="F53">
-        <v>6579.612</v>
+        <v>6708.624000000001</v>
       </c>
       <c r="G53">
         <v>672</v>
@@ -5761,45 +5761,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M53">
-        <v>473.0741028</v>
+        <v>508.5136992000001</v>
       </c>
       <c r="N53">
-        <v>357.1008971999998</v>
+        <v>321.6613007999998</v>
       </c>
       <c r="O53">
-        <v>89.27522429999995</v>
+        <v>80.41532519999994</v>
       </c>
       <c r="P53">
-        <v>267.8256728999999</v>
+        <v>241.2459755999998</v>
       </c>
       <c r="Q53">
-        <v>668.0256728999998</v>
+        <v>641.4459755999998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1221517623591566</v>
+        <v>0.1235190933469638</v>
       </c>
       <c r="T53">
-        <v>1.530368763389398</v>
+        <v>1.55777508078534</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.754851925071388</v>
+        <v>1.632551888584401</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08885116480654263</v>
+        <v>0.08885446605709854</v>
       </c>
       <c r="C54">
-        <v>4339.958077627417</v>
+        <v>4210.150441297686</v>
       </c>
       <c r="D54">
-        <v>10376.58207762742</v>
+        <v>10375.78644129769</v>
       </c>
       <c r="E54">
-        <v>858.1240000000007</v>
+        <v>987.1360000000004</v>
       </c>
       <c r="F54">
-        <v>6708.624000000001</v>
+        <v>6837.636</v>
       </c>
       <c r="G54">
         <v>672</v>
@@ -5843,28 +5843,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M54">
-        <v>508.5136992000001</v>
+        <v>518.2928088000001</v>
       </c>
       <c r="N54">
-        <v>321.6613007999998</v>
+        <v>311.8821911999997</v>
       </c>
       <c r="O54">
-        <v>80.41532519999994</v>
+        <v>77.97054779999993</v>
       </c>
       <c r="P54">
-        <v>241.2459755999998</v>
+        <v>233.9116433999998</v>
       </c>
       <c r="Q54">
-        <v>641.4459755999998</v>
+        <v>634.1116433999997</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1235190933469638</v>
+        <v>0.1249446086321246</v>
       </c>
       <c r="T54">
-        <v>1.55777508078534</v>
+        <v>1.586347624453449</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.632551888584401</v>
+        <v>1.601749022762053</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08885446605709854</v>
+        <v>0.08885776730765446</v>
       </c>
       <c r="C55">
-        <v>4210.150441297686</v>
+        <v>4080.342926971254</v>
       </c>
       <c r="D55">
-        <v>10375.78644129769</v>
+        <v>10374.99092697126</v>
       </c>
       <c r="E55">
-        <v>987.1360000000004</v>
+        <v>1116.148000000001</v>
       </c>
       <c r="F55">
-        <v>6837.636</v>
+        <v>6966.648000000001</v>
       </c>
       <c r="G55">
         <v>672</v>
@@ -5925,28 +5925,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M55">
-        <v>518.2928088000001</v>
+        <v>528.0719184000001</v>
       </c>
       <c r="N55">
-        <v>311.8821911999997</v>
+        <v>302.1030815999998</v>
       </c>
       <c r="O55">
-        <v>77.97054779999993</v>
+        <v>75.52577039999994</v>
       </c>
       <c r="P55">
-        <v>233.9116433999998</v>
+        <v>226.5773111999998</v>
       </c>
       <c r="Q55">
-        <v>634.1116433999997</v>
+        <v>626.7773111999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1249446086321246</v>
+        <v>0.1264321028427271</v>
       </c>
       <c r="T55">
-        <v>1.586347624453449</v>
+        <v>1.616162452628868</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.601749022762053</v>
+        <v>1.572087003822015</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08885776730765446</v>
+        <v>0.08886106855821038</v>
       </c>
       <c r="C56">
-        <v>4080.342926971254</v>
+        <v>3950.535534620062</v>
       </c>
       <c r="D56">
-        <v>10374.99092697126</v>
+        <v>10374.19553462006</v>
       </c>
       <c r="E56">
-        <v>1116.148000000001</v>
+        <v>1245.160000000001</v>
       </c>
       <c r="F56">
-        <v>6966.648000000001</v>
+        <v>7095.660000000001</v>
       </c>
       <c r="G56">
         <v>672</v>
@@ -6007,28 +6007,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M56">
-        <v>528.0719184000001</v>
+        <v>537.8510280000002</v>
       </c>
       <c r="N56">
-        <v>302.1030815999998</v>
+        <v>292.3239719999997</v>
       </c>
       <c r="O56">
-        <v>75.52577039999994</v>
+        <v>73.08099299999992</v>
       </c>
       <c r="P56">
-        <v>226.5773111999998</v>
+        <v>219.2429789999998</v>
       </c>
       <c r="Q56">
-        <v>626.7773111999998</v>
+        <v>619.4429789999997</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1264321028427271</v>
+        <v>0.1279857079071342</v>
       </c>
       <c r="T56">
-        <v>1.616162452628868</v>
+        <v>1.64730238427875</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.572087003822015</v>
+        <v>1.543503603752524</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08886106855821038</v>
+        <v>0.08886436980876627</v>
       </c>
       <c r="C57">
-        <v>3950.535534620062</v>
+        <v>3820.728264216067</v>
       </c>
       <c r="D57">
-        <v>10374.19553462006</v>
+        <v>10373.40026421607</v>
       </c>
       <c r="E57">
-        <v>1245.160000000001</v>
+        <v>1374.172000000001</v>
       </c>
       <c r="F57">
-        <v>7095.660000000001</v>
+        <v>7224.672000000001</v>
       </c>
       <c r="G57">
         <v>672</v>
@@ -6089,28 +6089,28 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M57">
-        <v>537.8510280000002</v>
+        <v>547.6301376000001</v>
       </c>
       <c r="N57">
-        <v>292.3239719999997</v>
+        <v>282.5448623999997</v>
       </c>
       <c r="O57">
-        <v>73.08099299999992</v>
+        <v>70.63621559999993</v>
       </c>
       <c r="P57">
-        <v>219.2429789999998</v>
+        <v>211.9086467999998</v>
       </c>
       <c r="Q57">
-        <v>619.4429789999997</v>
+        <v>612.1086467999997</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1279857079071342</v>
+        <v>0.1296099313835597</v>
       </c>
       <c r="T57">
-        <v>1.64730238427875</v>
+        <v>1.679857767367263</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.543503603752524</v>
+        <v>1.5159410393998</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08886436980876627</v>
+        <v>0.0949381710593222</v>
       </c>
       <c r="C58">
-        <v>3820.728264216067</v>
+        <v>2409.495739132857</v>
       </c>
       <c r="D58">
-        <v>10373.40026421607</v>
+        <v>9091.179739132858</v>
       </c>
       <c r="E58">
-        <v>1374.172000000001</v>
+        <v>1503.184000000001</v>
       </c>
       <c r="F58">
-        <v>7224.672000000001</v>
+        <v>7353.684000000001</v>
       </c>
       <c r="G58">
         <v>672</v>
@@ -6171,45 +6171,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M58">
-        <v>547.6301376000001</v>
+        <v>661.8315600000001</v>
       </c>
       <c r="N58">
-        <v>282.5448623999997</v>
+        <v>168.3434399999998</v>
       </c>
       <c r="O58">
-        <v>70.63621559999993</v>
+        <v>42.08585999999994</v>
       </c>
       <c r="P58">
-        <v>211.9086467999998</v>
+        <v>126.2575799999998</v>
       </c>
       <c r="Q58">
-        <v>612.1086467999997</v>
+        <v>526.4575799999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1296099313835597</v>
+        <v>0.1313097001379586</v>
       </c>
       <c r="T58">
-        <v>1.679857767367263</v>
+        <v>1.713927354320358</v>
       </c>
       <c r="U58">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.5159410393998</v>
+        <v>1.254359946207461</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0949381710593222</v>
+        <v>0.109000063280196</v>
       </c>
       <c r="C59">
-        <v>2409.495739132857</v>
+        <v>257.7137763006122</v>
       </c>
       <c r="D59">
-        <v>9091.179739132858</v>
+        <v>7068.409776300614</v>
       </c>
       <c r="E59">
-        <v>1503.184000000001</v>
+        <v>1632.196000000002</v>
       </c>
       <c r="F59">
-        <v>7353.684000000001</v>
+        <v>7482.696000000002</v>
       </c>
       <c r="G59">
         <v>672</v>
@@ -6253,45 +6253,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M59">
-        <v>661.8315600000001</v>
+        <v>887.4477456000003</v>
       </c>
       <c r="N59">
-        <v>168.3434399999998</v>
+        <v>-57.27274560000046</v>
       </c>
       <c r="O59">
-        <v>42.08585999999994</v>
+        <v>-14.31818640000012</v>
       </c>
       <c r="P59">
-        <v>126.2575799999998</v>
+        <v>-42.95455920000035</v>
       </c>
       <c r="Q59">
-        <v>526.4575799999998</v>
+        <v>357.2454407999996</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1313097001379586</v>
+        <v>0.1340457847388253</v>
       </c>
       <c r="T59">
-        <v>1.713927354320358</v>
+        <v>1.768768503729072</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.25</v>
+        <v>0.2338658822775873</v>
       </c>
       <c r="W59">
-        <v>0.0675</v>
+        <v>0.09086350636187815</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.254359946207461</v>
+        <v>0.9354635291103495</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1090000632801959</v>
+        <v>0.1097280632801959</v>
       </c>
       <c r="C60">
-        <v>257.7137763006167</v>
+        <v>48.20813934194848</v>
       </c>
       <c r="D60">
-        <v>7068.409776300617</v>
+        <v>6987.916139341948</v>
       </c>
       <c r="E60">
-        <v>1632.196</v>
+        <v>1761.208</v>
       </c>
       <c r="F60">
-        <v>7482.696</v>
+        <v>7611.708</v>
       </c>
       <c r="G60">
         <v>672</v>
@@ -6335,37 +6335,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M60">
-        <v>887.4477456000001</v>
+        <v>902.7485688</v>
       </c>
       <c r="N60">
-        <v>-57.27274560000023</v>
+        <v>-72.5735688000002</v>
       </c>
       <c r="O60">
-        <v>-14.31818640000006</v>
+        <v>-18.14339220000005</v>
       </c>
       <c r="P60">
-        <v>-42.95455920000018</v>
+        <v>-54.43017660000015</v>
       </c>
       <c r="Q60">
-        <v>357.2454407999998</v>
+        <v>345.7698233999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1340457847388253</v>
+        <v>0.1361981209519673</v>
       </c>
       <c r="T60">
-        <v>1.768768503729071</v>
+        <v>1.811909198941975</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.2338658822775874</v>
+        <v>0.229902053764408</v>
       </c>
       <c r="W60">
-        <v>0.09086350636187814</v>
+        <v>0.09133361642354122</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9354635291103497</v>
+        <v>0.9196082150576319</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1097280632801959</v>
+        <v>0.1104560632801959</v>
       </c>
       <c r="C61">
-        <v>48.20813934194848</v>
+        <v>-159.4848488183534</v>
       </c>
       <c r="D61">
-        <v>6987.916139341948</v>
+        <v>6909.235151181647</v>
       </c>
       <c r="E61">
-        <v>1761.208</v>
+        <v>1890.22</v>
       </c>
       <c r="F61">
-        <v>7611.708</v>
+        <v>7740.72</v>
       </c>
       <c r="G61">
         <v>672</v>
@@ -6417,37 +6417,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M61">
-        <v>902.7485688</v>
+        <v>918.0493920000001</v>
       </c>
       <c r="N61">
-        <v>-72.5735688000002</v>
+        <v>-87.87439200000028</v>
       </c>
       <c r="O61">
-        <v>-18.14339220000005</v>
+        <v>-21.96859800000007</v>
       </c>
       <c r="P61">
-        <v>-54.43017660000015</v>
+        <v>-65.90579400000021</v>
       </c>
       <c r="Q61">
-        <v>345.7698233999998</v>
+        <v>334.2942059999997</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1361981209519673</v>
+        <v>0.1384580739757665</v>
       </c>
       <c r="T61">
-        <v>1.811909198941975</v>
+        <v>1.857206928915524</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.229902053764408</v>
+        <v>0.2260703528683345</v>
       </c>
       <c r="W61">
-        <v>0.09133361642354122</v>
+        <v>0.09178805614981553</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9196082150576319</v>
+        <v>0.904281411473338</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1104560632801959</v>
+        <v>0.1111840632801959</v>
       </c>
       <c r="C62">
-        <v>-159.4848488183534</v>
+        <v>-365.4257354264728</v>
       </c>
       <c r="D62">
-        <v>6909.235151181647</v>
+        <v>6832.306264573527</v>
       </c>
       <c r="E62">
-        <v>1890.22</v>
+        <v>2019.232</v>
       </c>
       <c r="F62">
-        <v>7740.72</v>
+        <v>7869.732</v>
       </c>
       <c r="G62">
         <v>672</v>
@@ -6499,37 +6499,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M62">
-        <v>918.0493920000001</v>
+        <v>933.3502152000001</v>
       </c>
       <c r="N62">
-        <v>-87.87439200000028</v>
+        <v>-103.1752152000003</v>
       </c>
       <c r="O62">
-        <v>-21.96859800000007</v>
+        <v>-25.79380380000006</v>
       </c>
       <c r="P62">
-        <v>-65.90579400000021</v>
+        <v>-77.38141140000019</v>
       </c>
       <c r="Q62">
-        <v>334.2942059999997</v>
+        <v>322.8185885999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1384580739757665</v>
+        <v>0.1408339220264272</v>
       </c>
       <c r="T62">
-        <v>1.857206928915524</v>
+        <v>1.904827619400538</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.2260703528683345</v>
+        <v>0.2223642815098372</v>
       </c>
       <c r="W62">
-        <v>0.09178805614981553</v>
+        <v>0.09222759621293332</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.904281411473338</v>
+        <v>0.8894571260393488</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1111840632801959</v>
+        <v>0.111912063280196</v>
       </c>
       <c r="C63">
-        <v>-365.4257354264728</v>
+        <v>-569.6724008388856</v>
       </c>
       <c r="D63">
-        <v>6832.306264573527</v>
+        <v>6757.071599161115</v>
       </c>
       <c r="E63">
-        <v>2019.232</v>
+        <v>2148.244000000001</v>
       </c>
       <c r="F63">
-        <v>7869.732</v>
+        <v>7998.744000000001</v>
       </c>
       <c r="G63">
         <v>672</v>
@@ -6581,37 +6581,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M63">
-        <v>933.3502152000001</v>
+        <v>948.6510384000002</v>
       </c>
       <c r="N63">
-        <v>-103.1752152000003</v>
+        <v>-118.4760384000003</v>
       </c>
       <c r="O63">
-        <v>-25.79380380000006</v>
+        <v>-29.61900960000008</v>
       </c>
       <c r="P63">
-        <v>-77.38141140000019</v>
+        <v>-88.85702880000025</v>
       </c>
       <c r="Q63">
-        <v>322.8185885999998</v>
+        <v>311.3429711999997</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1408339220264272</v>
+        <v>0.1433348147113332</v>
       </c>
       <c r="T63">
-        <v>1.904827619400538</v>
+        <v>1.954954662016342</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.2223642815098372</v>
+        <v>0.2187777608403237</v>
       </c>
       <c r="W63">
-        <v>0.09222759621293332</v>
+        <v>0.09265295756433763</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8894571260393488</v>
+        <v>0.8751110433612947</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.111912063280196</v>
+        <v>0.1126400632801959</v>
       </c>
       <c r="C64">
-        <v>-569.6724008388856</v>
+        <v>-772.2802037567835</v>
       </c>
       <c r="D64">
-        <v>6757.071599161115</v>
+        <v>6683.475796243217</v>
       </c>
       <c r="E64">
-        <v>2148.244000000001</v>
+        <v>2277.256</v>
       </c>
       <c r="F64">
-        <v>7998.744000000001</v>
+        <v>8127.756</v>
       </c>
       <c r="G64">
         <v>672</v>
@@ -6663,37 +6663,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M64">
-        <v>948.6510384000002</v>
+        <v>963.9518616000001</v>
       </c>
       <c r="N64">
-        <v>-118.4760384000003</v>
+        <v>-133.7768616000003</v>
       </c>
       <c r="O64">
-        <v>-29.61900960000008</v>
+        <v>-33.44421540000008</v>
       </c>
       <c r="P64">
-        <v>-88.85702880000025</v>
+        <v>-100.3326462000002</v>
       </c>
       <c r="Q64">
-        <v>311.3429711999997</v>
+        <v>299.8673537999997</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1433348147113332</v>
+        <v>0.1459708907846125</v>
       </c>
       <c r="T64">
-        <v>1.954954662016342</v>
+        <v>2.00779127450327</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.2187777608403237</v>
+        <v>0.2153050979698424</v>
       </c>
       <c r="W64">
-        <v>0.09265295756433763</v>
+        <v>0.09306481538077671</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8751110433612947</v>
+        <v>0.8612203918793695</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1126400632801959</v>
+        <v>0.1133680632801959</v>
       </c>
       <c r="C65">
-        <v>-772.2802037567835</v>
+        <v>-973.3021170717211</v>
       </c>
       <c r="D65">
-        <v>6683.475796243217</v>
+        <v>6611.465882928279</v>
       </c>
       <c r="E65">
-        <v>2277.256</v>
+        <v>2406.268</v>
       </c>
       <c r="F65">
-        <v>8127.756</v>
+        <v>8256.768</v>
       </c>
       <c r="G65">
         <v>672</v>
@@ -6745,37 +6745,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M65">
-        <v>963.9518616000001</v>
+        <v>979.2526848000001</v>
       </c>
       <c r="N65">
-        <v>-133.7768616000003</v>
+        <v>-149.0776848000003</v>
       </c>
       <c r="O65">
-        <v>-33.44421540000008</v>
+        <v>-37.26942120000007</v>
       </c>
       <c r="P65">
-        <v>-100.3326462000002</v>
+        <v>-111.8082636000002</v>
       </c>
       <c r="Q65">
-        <v>299.8673537999997</v>
+        <v>288.3917363999997</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1459708907846125</v>
+        <v>0.1487534155286295</v>
       </c>
       <c r="T65">
-        <v>2.00779127450327</v>
+        <v>2.063563254350584</v>
       </c>
       <c r="U65">
         <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.2153050979698424</v>
+        <v>0.2119409558140636</v>
       </c>
       <c r="W65">
-        <v>0.09306481538077671</v>
+        <v>0.09346380264045206</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8612203918793695</v>
+        <v>0.8477638232562543</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1133680632801959</v>
+        <v>0.1140960632801959</v>
       </c>
       <c r="C66">
-        <v>-973.3021170717211</v>
+        <v>-1172.788855022942</v>
       </c>
       <c r="D66">
-        <v>6611.465882928279</v>
+        <v>6540.991144977059</v>
       </c>
       <c r="E66">
-        <v>2406.268</v>
+        <v>2535.280000000001</v>
       </c>
       <c r="F66">
-        <v>8256.768</v>
+        <v>8385.780000000001</v>
       </c>
       <c r="G66">
         <v>672</v>
@@ -6827,37 +6827,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M66">
-        <v>979.2526848000001</v>
+        <v>994.5535080000002</v>
       </c>
       <c r="N66">
-        <v>-149.0776848000003</v>
+        <v>-164.3785080000004</v>
       </c>
       <c r="O66">
-        <v>-37.26942120000007</v>
+        <v>-41.09462700000009</v>
       </c>
       <c r="P66">
-        <v>-111.8082636000002</v>
+        <v>-123.2838810000003</v>
       </c>
       <c r="Q66">
-        <v>288.3917363999997</v>
+        <v>276.9161189999996</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1487534155286295</v>
+        <v>0.1516949416865903</v>
       </c>
       <c r="T66">
-        <v>2.063563254350584</v>
+        <v>2.122522204474886</v>
       </c>
       <c r="U66">
         <v>0.1186</v>
       </c>
       <c r="V66">
-        <v>0.2119409558140636</v>
+        <v>0.2086803257246165</v>
       </c>
       <c r="W66">
-        <v>0.09346380264045206</v>
+        <v>0.0938505133690605</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8477638232562543</v>
+        <v>0.8347213028984657</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1140960632801959</v>
+        <v>0.114824063280196</v>
       </c>
       <c r="C67">
-        <v>-1172.788855022942</v>
+        <v>-1370.788992307952</v>
       </c>
       <c r="D67">
-        <v>6540.991144977059</v>
+        <v>6472.003007692049</v>
       </c>
       <c r="E67">
-        <v>2535.280000000001</v>
+        <v>2664.292000000001</v>
       </c>
       <c r="F67">
-        <v>8385.780000000001</v>
+        <v>8514.792000000001</v>
       </c>
       <c r="G67">
         <v>672</v>
@@ -6909,37 +6909,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M67">
-        <v>994.5535080000002</v>
+        <v>1009.8543312</v>
       </c>
       <c r="N67">
-        <v>-164.3785080000004</v>
+        <v>-179.6793312000004</v>
       </c>
       <c r="O67">
-        <v>-41.09462700000009</v>
+        <v>-44.91983280000011</v>
       </c>
       <c r="P67">
-        <v>-123.2838810000003</v>
+        <v>-134.7594984000003</v>
       </c>
       <c r="Q67">
-        <v>276.9161189999996</v>
+        <v>265.4405015999996</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1516949416865903</v>
+        <v>0.1548094987950195</v>
       </c>
       <c r="T67">
-        <v>2.122522204474886</v>
+        <v>2.184949328135912</v>
       </c>
       <c r="U67">
         <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.2086803257246165</v>
+        <v>0.2055185026075768</v>
       </c>
       <c r="W67">
-        <v>0.0938505133690605</v>
+        <v>0.0942255055907414</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8347213028984657</v>
+        <v>0.8220740104303071</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.114824063280196</v>
+        <v>0.1155520632801959</v>
       </c>
       <c r="C68">
-        <v>-1370.788992307952</v>
+        <v>-1567.349075734145</v>
       </c>
       <c r="D68">
-        <v>6472.003007692049</v>
+        <v>6404.454924265857</v>
       </c>
       <c r="E68">
-        <v>2664.292000000001</v>
+        <v>2793.304000000002</v>
       </c>
       <c r="F68">
-        <v>8514.792000000001</v>
+        <v>8643.804000000002</v>
       </c>
       <c r="G68">
         <v>672</v>
@@ -6991,37 +6991,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M68">
-        <v>1009.8543312</v>
+        <v>1025.1551544</v>
       </c>
       <c r="N68">
-        <v>-179.6793312000004</v>
+        <v>-194.9801544000005</v>
       </c>
       <c r="O68">
-        <v>-44.91983280000011</v>
+        <v>-48.74503860000013</v>
       </c>
       <c r="P68">
-        <v>-134.7594984000003</v>
+        <v>-146.2351158000004</v>
       </c>
       <c r="Q68">
-        <v>265.4405015999996</v>
+        <v>253.9648841999995</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1548094987950195</v>
+        <v>0.1581128169403231</v>
       </c>
       <c r="T68">
-        <v>2.184949328135912</v>
+        <v>2.251159913837</v>
       </c>
       <c r="U68">
         <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2055185026075768</v>
+        <v>0.2024510622701503</v>
       </c>
       <c r="W68">
-        <v>0.0942255055907414</v>
+        <v>0.09458930401476018</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8220740104303071</v>
+        <v>0.809804249080601</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1155520632801959</v>
+        <v>0.1745570264744111</v>
       </c>
       <c r="C69">
-        <v>-1567.349075734145</v>
+        <v>-4631.304802167739</v>
       </c>
       <c r="D69">
-        <v>6404.454924265857</v>
+        <v>3469.511197832262</v>
       </c>
       <c r="E69">
-        <v>2793.304000000002</v>
+        <v>2922.316000000001</v>
       </c>
       <c r="F69">
-        <v>8643.804000000002</v>
+        <v>8772.816000000001</v>
       </c>
       <c r="G69">
         <v>672</v>
@@ -7073,45 +7073,45 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M69">
-        <v>1025.1551544</v>
+        <v>1761.5814528</v>
       </c>
       <c r="N69">
-        <v>-194.9801544000005</v>
+        <v>-931.4064528000005</v>
       </c>
       <c r="O69">
-        <v>-48.74503860000013</v>
+        <v>-232.8516132000001</v>
       </c>
       <c r="P69">
-        <v>-146.2351158000004</v>
+        <v>-698.5548396000004</v>
       </c>
       <c r="Q69">
-        <v>253.9648841999995</v>
+        <v>-298.3548396000004</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1581128169403231</v>
+        <v>0.1690631024516307</v>
       </c>
       <c r="T69">
-        <v>2.251159913837</v>
+        <v>2.470643713279265</v>
       </c>
       <c r="U69">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.2024510622701503</v>
+        <v>0.1178167206915769</v>
       </c>
       <c r="W69">
-        <v>0.09458930401476018</v>
+        <v>0.1771424024851314</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.809804249080601</v>
+        <v>0.4712668827663078</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1745570264744111</v>
+        <v>0.1761070264744111</v>
       </c>
       <c r="C70">
-        <v>-4631.304802167739</v>
+        <v>-4801.586582486884</v>
       </c>
       <c r="D70">
-        <v>3469.511197832262</v>
+        <v>3428.241417513117</v>
       </c>
       <c r="E70">
-        <v>2922.316000000001</v>
+        <v>3051.328000000001</v>
       </c>
       <c r="F70">
-        <v>8772.816000000001</v>
+        <v>8901.828000000001</v>
       </c>
       <c r="G70">
         <v>672</v>
@@ -7155,37 +7155,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M70">
-        <v>1761.5814528</v>
+        <v>1787.4870624</v>
       </c>
       <c r="N70">
-        <v>-931.4064528000005</v>
+        <v>-957.3120624000004</v>
       </c>
       <c r="O70">
-        <v>-232.8516132000001</v>
+        <v>-239.3280156000001</v>
       </c>
       <c r="P70">
-        <v>-698.5548396000004</v>
+        <v>-717.9840468000003</v>
       </c>
       <c r="Q70">
-        <v>-298.3548396000004</v>
+        <v>-317.7840468000004</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1690631024516307</v>
+        <v>0.1730393315629736</v>
       </c>
       <c r="T70">
-        <v>2.470643713279265</v>
+        <v>2.550341897578597</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1178167206915769</v>
+        <v>0.1161092319859019</v>
       </c>
       <c r="W70">
-        <v>0.1771424024851314</v>
+        <v>0.1774852662172309</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4712668827663078</v>
+        <v>0.4644369279436077</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1761070264744111</v>
+        <v>0.1776570264744111</v>
       </c>
       <c r="C71">
-        <v>-4801.586582486884</v>
+        <v>-4970.898097341913</v>
       </c>
       <c r="D71">
-        <v>3428.241417513117</v>
+        <v>3387.941902658089</v>
       </c>
       <c r="E71">
-        <v>3051.328000000001</v>
+        <v>3180.340000000002</v>
       </c>
       <c r="F71">
-        <v>8901.828000000001</v>
+        <v>9030.840000000002</v>
       </c>
       <c r="G71">
         <v>672</v>
@@ -7237,37 +7237,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M71">
-        <v>1787.4870624</v>
+        <v>1813.392672</v>
       </c>
       <c r="N71">
-        <v>-957.3120624000004</v>
+        <v>-983.2176720000006</v>
       </c>
       <c r="O71">
-        <v>-239.3280156000001</v>
+        <v>-245.8044180000001</v>
       </c>
       <c r="P71">
-        <v>-717.9840468000003</v>
+        <v>-737.4132540000004</v>
       </c>
       <c r="Q71">
-        <v>-317.7840468000004</v>
+        <v>-337.2132540000005</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1730393315629736</v>
+        <v>0.1772806426150727</v>
       </c>
       <c r="T71">
-        <v>2.550341897578597</v>
+        <v>2.63535329416455</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1161092319859019</v>
+        <v>0.1144505286718176</v>
       </c>
       <c r="W71">
-        <v>0.1774852662172309</v>
+        <v>0.177818333842699</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4644369279436077</v>
+        <v>0.4578021146872704</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1776570264744111</v>
+        <v>0.1792070264744111</v>
       </c>
       <c r="C72">
-        <v>-4970.898097341913</v>
+        <v>-5139.273166048995</v>
       </c>
       <c r="D72">
-        <v>3387.941902658089</v>
+        <v>3348.578833951005</v>
       </c>
       <c r="E72">
-        <v>3180.340000000002</v>
+        <v>3309.352000000001</v>
       </c>
       <c r="F72">
-        <v>9030.840000000002</v>
+        <v>9159.852000000001</v>
       </c>
       <c r="G72">
         <v>672</v>
@@ -7319,37 +7319,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M72">
-        <v>1813.392672</v>
+        <v>1839.2982816</v>
       </c>
       <c r="N72">
-        <v>-983.2176720000006</v>
+        <v>-1009.1232816</v>
       </c>
       <c r="O72">
-        <v>-245.8044180000001</v>
+        <v>-252.2808204000001</v>
       </c>
       <c r="P72">
-        <v>-737.4132540000004</v>
+        <v>-756.8424612000002</v>
       </c>
       <c r="Q72">
-        <v>-337.2132540000005</v>
+        <v>-356.6424612000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1772806426150727</v>
+        <v>0.1818144578776615</v>
       </c>
       <c r="T72">
-        <v>2.63535329416455</v>
+        <v>2.726227545687466</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1144505286718176</v>
+        <v>0.1128385493947498</v>
       </c>
       <c r="W72">
-        <v>0.177818333842699</v>
+        <v>0.1781420192815343</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4578021146872704</v>
+        <v>0.451354197578999</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1792070264744111</v>
+        <v>0.1807570264744111</v>
       </c>
       <c r="C73">
-        <v>-5139.273166048995</v>
+        <v>-5306.744054246329</v>
       </c>
       <c r="D73">
-        <v>3348.578833951005</v>
+        <v>3310.11994575367</v>
       </c>
       <c r="E73">
-        <v>3309.352000000001</v>
+        <v>3438.364</v>
       </c>
       <c r="F73">
-        <v>9159.852000000001</v>
+        <v>9288.864</v>
       </c>
       <c r="G73">
         <v>672</v>
@@ -7401,37 +7401,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M73">
-        <v>1839.2982816</v>
+        <v>1865.2038912</v>
       </c>
       <c r="N73">
-        <v>-1009.1232816</v>
+        <v>-1035.0288912</v>
       </c>
       <c r="O73">
-        <v>-252.2808204000001</v>
+        <v>-258.7572228</v>
       </c>
       <c r="P73">
-        <v>-756.8424612000002</v>
+        <v>-776.2716684000001</v>
       </c>
       <c r="Q73">
-        <v>-356.6424612000003</v>
+        <v>-376.0716684000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1818144578776614</v>
+        <v>0.1866721170875779</v>
       </c>
       <c r="T73">
-        <v>2.726227545687465</v>
+        <v>2.823592815176303</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1128385493947498</v>
+        <v>0.1112713473198227</v>
       </c>
       <c r="W73">
-        <v>0.1781420192815343</v>
+        <v>0.1784567134581796</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.451354197578999</v>
+        <v>0.4450853892792908</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1807570264744111</v>
+        <v>0.1823070264744111</v>
       </c>
       <c r="C74">
-        <v>-5306.744054246329</v>
+        <v>-5473.341562102073</v>
       </c>
       <c r="D74">
-        <v>3310.11994575367</v>
+        <v>3272.534437897927</v>
       </c>
       <c r="E74">
-        <v>3438.364</v>
+        <v>3567.376</v>
       </c>
       <c r="F74">
-        <v>9288.864</v>
+        <v>9417.876</v>
       </c>
       <c r="G74">
         <v>672</v>
@@ -7483,37 +7483,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M74">
-        <v>1865.2038912</v>
+        <v>1891.1095008</v>
       </c>
       <c r="N74">
-        <v>-1035.0288912</v>
+        <v>-1060.9345008</v>
       </c>
       <c r="O74">
-        <v>-258.7572228</v>
+        <v>-265.2336252000001</v>
       </c>
       <c r="P74">
-        <v>-776.2716684000001</v>
+        <v>-795.7008756000004</v>
       </c>
       <c r="Q74">
-        <v>-376.0716684000001</v>
+        <v>-395.5008756000004</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1866721170875779</v>
+        <v>0.1918896029056363</v>
       </c>
       <c r="T74">
-        <v>2.823592815176303</v>
+        <v>2.928170326849499</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1112713473198227</v>
+        <v>0.1097470822880443</v>
       </c>
       <c r="W74">
-        <v>0.1784567134581796</v>
+        <v>0.1787627858765607</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4450853892792908</v>
+        <v>0.438988329152177</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1823070264744111</v>
+        <v>0.1838570264744111</v>
       </c>
       <c r="C75">
-        <v>-5473.341562102073</v>
+        <v>-5639.095106580303</v>
       </c>
       <c r="D75">
-        <v>3272.534437897927</v>
+        <v>3235.792893419698</v>
       </c>
       <c r="E75">
-        <v>3567.376</v>
+        <v>3696.388000000001</v>
       </c>
       <c r="F75">
-        <v>9417.876</v>
+        <v>9546.888000000001</v>
       </c>
       <c r="G75">
         <v>672</v>
@@ -7565,37 +7565,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M75">
-        <v>1891.1095008</v>
+        <v>1917.0151104</v>
       </c>
       <c r="N75">
-        <v>-1060.9345008</v>
+        <v>-1086.8401104</v>
       </c>
       <c r="O75">
-        <v>-265.2336252000001</v>
+        <v>-271.7100276000001</v>
       </c>
       <c r="P75">
-        <v>-795.7008756000004</v>
+        <v>-815.1300828000003</v>
       </c>
       <c r="Q75">
-        <v>-395.5008756000004</v>
+        <v>-414.9300828000004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1918896029056363</v>
+        <v>0.1975084337866223</v>
       </c>
       <c r="T75">
-        <v>2.928170326849499</v>
+        <v>3.040792262497557</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1097470822880443</v>
+        <v>0.1082640136084761</v>
       </c>
       <c r="W75">
-        <v>0.1787627858765607</v>
+        <v>0.179060586067418</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.438988329152177</v>
+        <v>0.4330560544339044</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1838570264744111</v>
+        <v>0.1854070264744111</v>
       </c>
       <c r="C76">
-        <v>-5639.095106580303</v>
+        <v>-5804.032798226777</v>
       </c>
       <c r="D76">
-        <v>3235.792893419698</v>
+        <v>3199.867201773225</v>
       </c>
       <c r="E76">
-        <v>3696.388000000001</v>
+        <v>3825.400000000001</v>
       </c>
       <c r="F76">
-        <v>9546.888000000001</v>
+        <v>9675.900000000001</v>
       </c>
       <c r="G76">
         <v>672</v>
@@ -7647,37 +7647,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M76">
-        <v>1917.0151104</v>
+        <v>1942.92072</v>
       </c>
       <c r="N76">
-        <v>-1086.8401104</v>
+        <v>-1112.74572</v>
       </c>
       <c r="O76">
-        <v>-271.7100276000001</v>
+        <v>-278.1864300000001</v>
       </c>
       <c r="P76">
-        <v>-815.1300828000003</v>
+        <v>-834.5592900000003</v>
       </c>
       <c r="Q76">
-        <v>-414.9300828000004</v>
+        <v>-434.3592900000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1975084337866223</v>
+        <v>0.2035767711380872</v>
       </c>
       <c r="T76">
-        <v>3.040792262497557</v>
+        <v>3.162423952997459</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1082640136084761</v>
+        <v>0.1068204934270298</v>
       </c>
       <c r="W76">
-        <v>0.179060586067418</v>
+        <v>0.1793504449198524</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4330560544339044</v>
+        <v>0.427281973708119</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1854070264744111</v>
+        <v>0.1869570264744111</v>
       </c>
       <c r="C77">
-        <v>-5804.032798226777</v>
+        <v>-5968.181512895722</v>
       </c>
       <c r="D77">
-        <v>3199.867201773225</v>
+        <v>3164.730487104277</v>
       </c>
       <c r="E77">
-        <v>3825.400000000001</v>
+        <v>3954.412</v>
       </c>
       <c r="F77">
-        <v>9675.900000000001</v>
+        <v>9804.912</v>
       </c>
       <c r="G77">
         <v>672</v>
@@ -7729,37 +7729,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M77">
-        <v>1942.92072</v>
+        <v>1968.8263296</v>
       </c>
       <c r="N77">
-        <v>-1112.74572</v>
+        <v>-1138.6513296</v>
       </c>
       <c r="O77">
-        <v>-278.1864300000001</v>
+        <v>-284.6628324000001</v>
       </c>
       <c r="P77">
-        <v>-834.5592900000003</v>
+        <v>-853.9884972000002</v>
       </c>
       <c r="Q77">
-        <v>-434.3592900000003</v>
+        <v>-453.7884972000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2035767711380872</v>
+        <v>0.2101508032688409</v>
       </c>
       <c r="T77">
-        <v>3.162423952997459</v>
+        <v>3.294191617705687</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1068204934270298</v>
+        <v>0.1054149606187794</v>
       </c>
       <c r="W77">
-        <v>0.1793504449198524</v>
+        <v>0.1796326759077491</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.427281973708119</v>
+        <v>0.4216598424751175</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1869570264744111</v>
+        <v>0.1885070264744111</v>
       </c>
       <c r="C78">
-        <v>-5968.181512895722</v>
+        <v>-6131.566958802336</v>
       </c>
       <c r="D78">
-        <v>3164.730487104277</v>
+        <v>3130.357041197665</v>
       </c>
       <c r="E78">
-        <v>3954.412</v>
+        <v>4083.424000000001</v>
       </c>
       <c r="F78">
-        <v>9804.912</v>
+        <v>9933.924000000001</v>
       </c>
       <c r="G78">
         <v>672</v>
@@ -7811,37 +7811,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M78">
-        <v>1968.8263296</v>
+        <v>1994.7319392</v>
       </c>
       <c r="N78">
-        <v>-1138.6513296</v>
+        <v>-1164.5569392</v>
       </c>
       <c r="O78">
-        <v>-284.6628324000001</v>
+        <v>-291.1392348000001</v>
       </c>
       <c r="P78">
-        <v>-853.9884972000002</v>
+        <v>-873.4177044000002</v>
       </c>
       <c r="Q78">
-        <v>-453.7884972000003</v>
+        <v>-473.2177044000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2101508032688409</v>
+        <v>0.2172964903674861</v>
       </c>
       <c r="T78">
-        <v>3.294191617705687</v>
+        <v>3.43741734021463</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1054149606187794</v>
+        <v>0.1040459351561978</v>
       </c>
       <c r="W78">
-        <v>0.1796326759077491</v>
+        <v>0.1799075762206355</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4216598424751175</v>
+        <v>0.4161837406247914</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1885070264744111</v>
+        <v>0.1900570264744111</v>
       </c>
       <c r="C79">
-        <v>-6131.566958802336</v>
+        <v>-6294.213739252474</v>
       </c>
       <c r="D79">
-        <v>3130.357041197665</v>
+        <v>3096.722260747528</v>
       </c>
       <c r="E79">
-        <v>4083.424000000001</v>
+        <v>4212.436000000002</v>
       </c>
       <c r="F79">
-        <v>9933.924000000001</v>
+        <v>10062.936</v>
       </c>
       <c r="G79">
         <v>672</v>
@@ -7893,37 +7893,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M79">
-        <v>1994.7319392</v>
+        <v>2020.6375488</v>
       </c>
       <c r="N79">
-        <v>-1164.5569392</v>
+        <v>-1190.462548800001</v>
       </c>
       <c r="O79">
-        <v>-291.1392348000001</v>
+        <v>-297.6156372000002</v>
       </c>
       <c r="P79">
-        <v>-873.4177044000002</v>
+        <v>-892.8469116000005</v>
       </c>
       <c r="Q79">
-        <v>-473.2177044000002</v>
+        <v>-492.6469116000005</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2172964903674861</v>
+        <v>0.2250917853841901</v>
       </c>
       <c r="T79">
-        <v>3.43741734021463</v>
+        <v>3.593663582951658</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1040459351561978</v>
+        <v>0.1027120129106055</v>
       </c>
       <c r="W79">
-        <v>0.1799075762206355</v>
+        <v>0.1801754278075504</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4161837406247914</v>
+        <v>0.4108480516424221</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1900570264744111</v>
+        <v>0.1916070264744111</v>
       </c>
       <c r="C80">
-        <v>-6294.213739252474</v>
+        <v>-6456.145411371299</v>
       </c>
       <c r="D80">
-        <v>3096.722260747528</v>
+        <v>3063.802588628701</v>
       </c>
       <c r="E80">
-        <v>4212.436000000002</v>
+        <v>4341.448</v>
       </c>
       <c r="F80">
-        <v>10062.936</v>
+        <v>10191.948</v>
       </c>
       <c r="G80">
         <v>672</v>
@@ -7975,37 +7975,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M80">
-        <v>2020.6375488</v>
+        <v>2046.5431584</v>
       </c>
       <c r="N80">
-        <v>-1190.462548800001</v>
+        <v>-1216.3681584</v>
       </c>
       <c r="O80">
-        <v>-297.6156372000002</v>
+        <v>-304.0920396</v>
       </c>
       <c r="P80">
-        <v>-892.8469116000005</v>
+        <v>-912.2761188000001</v>
       </c>
       <c r="Q80">
-        <v>-492.6469116000005</v>
+        <v>-512.0761188000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2250917853841901</v>
+        <v>0.2336294894501039</v>
       </c>
       <c r="T80">
-        <v>3.593663582951658</v>
+        <v>3.764790420235072</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1027120129106055</v>
+        <v>0.101411860848446</v>
       </c>
       <c r="W80">
-        <v>0.1801754278075504</v>
+        <v>0.1804364983416321</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4108480516424221</v>
+        <v>0.405647443393784</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1916070264744111</v>
+        <v>0.1931570264744111</v>
       </c>
       <c r="C81">
-        <v>-6456.145411371299</v>
+        <v>-6617.384541125435</v>
       </c>
       <c r="D81">
-        <v>3063.802588628701</v>
+        <v>3031.575458874566</v>
       </c>
       <c r="E81">
-        <v>4341.448</v>
+        <v>4470.460000000001</v>
       </c>
       <c r="F81">
-        <v>10191.948</v>
+        <v>10320.96</v>
       </c>
       <c r="G81">
         <v>672</v>
@@ -8057,37 +8057,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M81">
-        <v>2046.5431584</v>
+        <v>2072.448768</v>
       </c>
       <c r="N81">
-        <v>-1216.3681584</v>
+        <v>-1242.273768</v>
       </c>
       <c r="O81">
-        <v>-304.0920396</v>
+        <v>-310.5684420000001</v>
       </c>
       <c r="P81">
-        <v>-912.2761188000001</v>
+        <v>-931.7053260000004</v>
       </c>
       <c r="Q81">
-        <v>-512.0761188000001</v>
+        <v>-531.5053260000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2336294894501039</v>
+        <v>0.2430209639226091</v>
       </c>
       <c r="T81">
-        <v>3.764790420235072</v>
+        <v>3.953029941246825</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.101411860848446</v>
+        <v>0.1001442125878404</v>
       </c>
       <c r="W81">
-        <v>0.1804364983416321</v>
+        <v>0.1806910421123616</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.405647443393784</v>
+        <v>0.4005768503513616</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1931570264744111</v>
+        <v>0.1947070264744112</v>
       </c>
       <c r="C82">
-        <v>-6617.384541125435</v>
+        <v>-6777.952754908693</v>
       </c>
       <c r="D82">
-        <v>3031.575458874566</v>
+        <v>3000.019245091308</v>
       </c>
       <c r="E82">
-        <v>4470.460000000001</v>
+        <v>4599.472000000002</v>
       </c>
       <c r="F82">
-        <v>10320.96</v>
+        <v>10449.972</v>
       </c>
       <c r="G82">
         <v>672</v>
@@ -8139,37 +8139,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M82">
-        <v>2072.448768</v>
+        <v>2098.354377600001</v>
       </c>
       <c r="N82">
-        <v>-1242.273768</v>
+        <v>-1268.179377600001</v>
       </c>
       <c r="O82">
-        <v>-310.5684420000001</v>
+        <v>-317.0448444000002</v>
       </c>
       <c r="P82">
-        <v>-931.7053260000004</v>
+        <v>-951.1345332000006</v>
       </c>
       <c r="Q82">
-        <v>-531.5053260000004</v>
+        <v>-550.9345332000007</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2430209639226091</v>
+        <v>0.253401014655378</v>
       </c>
       <c r="T82">
-        <v>3.953029941246825</v>
+        <v>4.161084148680869</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1001442125878404</v>
+        <v>0.0989078642842868</v>
       </c>
       <c r="W82">
-        <v>0.1806910421123616</v>
+        <v>0.1809393008517152</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4005768503513616</v>
+        <v>0.3956314571371472</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1947070264744112</v>
+        <v>0.1962570264744111</v>
       </c>
       <c r="C83">
-        <v>-6777.952754908693</v>
+        <v>-6937.87078793921</v>
       </c>
       <c r="D83">
-        <v>3000.019245091308</v>
+        <v>2969.113212060792</v>
       </c>
       <c r="E83">
-        <v>4599.472000000002</v>
+        <v>4728.484000000002</v>
       </c>
       <c r="F83">
-        <v>10449.972</v>
+        <v>10578.984</v>
       </c>
       <c r="G83">
         <v>672</v>
@@ -8221,37 +8221,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M83">
-        <v>2098.354377600001</v>
+        <v>2124.259987200001</v>
       </c>
       <c r="N83">
-        <v>-1268.179377600001</v>
+        <v>-1294.084987200001</v>
       </c>
       <c r="O83">
-        <v>-317.0448444000002</v>
+        <v>-323.5212468000002</v>
       </c>
       <c r="P83">
-        <v>-951.1345332000006</v>
+        <v>-970.5637404000006</v>
       </c>
       <c r="Q83">
-        <v>-550.9345332000007</v>
+        <v>-570.3637404000007</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.253401014655378</v>
+        <v>0.2649344043584546</v>
       </c>
       <c r="T83">
-        <v>4.161084148680869</v>
+        <v>4.392255490274251</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.0989078642842868</v>
+        <v>0.09770167081740526</v>
       </c>
       <c r="W83">
-        <v>0.1809393008517152</v>
+        <v>0.181181504499865</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3956314571371472</v>
+        <v>0.390806683269621</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1962570264744111</v>
+        <v>0.1978070264744111</v>
       </c>
       <c r="C84">
-        <v>-6937.87078793921</v>
+        <v>-7097.158529695586</v>
       </c>
       <c r="D84">
-        <v>2969.113212060792</v>
+        <v>2938.837470304415</v>
       </c>
       <c r="E84">
-        <v>4728.484000000002</v>
+        <v>4857.496000000001</v>
       </c>
       <c r="F84">
-        <v>10578.984</v>
+        <v>10707.996</v>
       </c>
       <c r="G84">
         <v>672</v>
@@ -8303,37 +8303,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M84">
-        <v>2124.259987200001</v>
+        <v>2150.1655968</v>
       </c>
       <c r="N84">
-        <v>-1294.084987200001</v>
+        <v>-1319.990596800001</v>
       </c>
       <c r="O84">
-        <v>-323.5212468000002</v>
+        <v>-329.9976492000002</v>
       </c>
       <c r="P84">
-        <v>-970.5637404000006</v>
+        <v>-989.9929476000005</v>
       </c>
       <c r="Q84">
-        <v>-570.3637404000007</v>
+        <v>-589.7929476000006</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2649344043584546</v>
+        <v>0.2778246634383637</v>
       </c>
       <c r="T84">
-        <v>4.392255490274251</v>
+        <v>4.650623460290383</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.09770167081740526</v>
+        <v>0.09652454225334015</v>
       </c>
       <c r="W84">
-        <v>0.181181504499865</v>
+        <v>0.1814178719155293</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.390806683269621</v>
+        <v>0.3860981690133605</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1978070264744111</v>
+        <v>0.1993570264744111</v>
       </c>
       <c r="C85">
-        <v>-7097.158529695586</v>
+        <v>-7255.835066601237</v>
       </c>
       <c r="D85">
-        <v>2938.837470304415</v>
+        <v>2909.172933398765</v>
       </c>
       <c r="E85">
-        <v>4857.496000000001</v>
+        <v>4986.508000000002</v>
       </c>
       <c r="F85">
-        <v>10707.996</v>
+        <v>10837.008</v>
       </c>
       <c r="G85">
         <v>672</v>
@@ -8385,37 +8385,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M85">
-        <v>2150.1655968</v>
+        <v>2176.0712064</v>
       </c>
       <c r="N85">
-        <v>-1319.990596800001</v>
+        <v>-1345.896206400001</v>
       </c>
       <c r="O85">
-        <v>-329.9976492000002</v>
+        <v>-336.4740516000002</v>
       </c>
       <c r="P85">
-        <v>-989.9929476000005</v>
+        <v>-1009.4221548</v>
       </c>
       <c r="Q85">
-        <v>-589.7929476000006</v>
+        <v>-609.2221548000006</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2778246634383637</v>
+        <v>0.2923262049032614</v>
       </c>
       <c r="T85">
-        <v>4.650623460290383</v>
+        <v>4.941287426558532</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.09652454225334015</v>
+        <v>0.09537544055984799</v>
       </c>
       <c r="W85">
-        <v>0.1814178719155293</v>
+        <v>0.1816486115355825</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3860981690133605</v>
+        <v>0.3815017622393919</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1993570264744111</v>
+        <v>0.2009070264744111</v>
       </c>
       <c r="C86">
-        <v>-7255.835066601235</v>
+        <v>-7413.918722149425</v>
       </c>
       <c r="D86">
-        <v>2909.172933398765</v>
+        <v>2880.101277850576</v>
       </c>
       <c r="E86">
-        <v>4986.508</v>
+        <v>5115.52</v>
       </c>
       <c r="F86">
-        <v>10837.008</v>
+        <v>10966.02</v>
       </c>
       <c r="G86">
         <v>672</v>
@@ -8467,37 +8467,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M86">
-        <v>2176.0712064</v>
+        <v>2201.976816</v>
       </c>
       <c r="N86">
-        <v>-1345.8962064</v>
+        <v>-1371.801816000001</v>
       </c>
       <c r="O86">
-        <v>-336.4740516000001</v>
+        <v>-342.9504540000001</v>
       </c>
       <c r="P86">
-        <v>-1009.4221548</v>
+        <v>-1028.851362</v>
       </c>
       <c r="Q86">
-        <v>-609.2221548000002</v>
+        <v>-628.6513620000004</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2923262049032613</v>
+        <v>0.3087612852301453</v>
       </c>
       <c r="T86">
-        <v>4.94128742655853</v>
+        <v>5.270706588329098</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.09537544055984802</v>
+        <v>0.09425337655326155</v>
       </c>
       <c r="W86">
-        <v>0.1816486115355825</v>
+        <v>0.1818739219881051</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.381501762239392</v>
+        <v>0.3770135062130462</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2009070264744111</v>
+        <v>0.2024570264744111</v>
       </c>
       <c r="C87">
-        <v>-7413.918722149425</v>
+        <v>-7571.427094646306</v>
       </c>
       <c r="D87">
-        <v>2880.101277850576</v>
+        <v>2851.604905353695</v>
       </c>
       <c r="E87">
-        <v>5115.52</v>
+        <v>5244.532000000001</v>
       </c>
       <c r="F87">
-        <v>10966.02</v>
+        <v>11095.032</v>
       </c>
       <c r="G87">
         <v>672</v>
@@ -8549,37 +8549,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M87">
-        <v>2201.976816</v>
+        <v>2227.8824256</v>
       </c>
       <c r="N87">
-        <v>-1371.801816000001</v>
+        <v>-1397.707425600001</v>
       </c>
       <c r="O87">
-        <v>-342.9504540000001</v>
+        <v>-349.4268564000001</v>
       </c>
       <c r="P87">
-        <v>-1028.851362</v>
+        <v>-1048.2805692</v>
       </c>
       <c r="Q87">
-        <v>-628.6513620000004</v>
+        <v>-648.0805692000005</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3087612852301453</v>
+        <v>0.3275442341751557</v>
       </c>
       <c r="T87">
-        <v>5.270706588329098</v>
+        <v>5.647185630352605</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.09425337655326155</v>
+        <v>0.0931574070584562</v>
       </c>
       <c r="W87">
-        <v>0.1818739219881051</v>
+        <v>0.182093992662662</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3770135062130462</v>
+        <v>0.3726296282338247</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2024570264744111</v>
+        <v>0.2040070264744111</v>
       </c>
       <c r="C88">
-        <v>-7571.427094646306</v>
+        <v>-7728.37709273524</v>
       </c>
       <c r="D88">
-        <v>2851.604905353695</v>
+        <v>2823.66690726476</v>
       </c>
       <c r="E88">
-        <v>5244.532000000001</v>
+        <v>5373.544</v>
       </c>
       <c r="F88">
-        <v>11095.032</v>
+        <v>11224.044</v>
       </c>
       <c r="G88">
         <v>672</v>
@@ -8631,37 +8631,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M88">
-        <v>2227.8824256</v>
+        <v>2253.7880352</v>
       </c>
       <c r="N88">
-        <v>-1397.707425600001</v>
+        <v>-1423.6130352</v>
       </c>
       <c r="O88">
-        <v>-349.4268564000001</v>
+        <v>-355.9032588000001</v>
       </c>
       <c r="P88">
-        <v>-1048.2805692</v>
+        <v>-1067.7097764</v>
       </c>
       <c r="Q88">
-        <v>-648.0805692000005</v>
+        <v>-667.5097764000005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3275442341751557</v>
+        <v>0.3492168675732447</v>
       </c>
       <c r="T88">
-        <v>5.647185630352605</v>
+        <v>6.081584524995113</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.0931574070584562</v>
+        <v>0.09208663226468083</v>
       </c>
       <c r="W88">
-        <v>0.182093992662662</v>
+        <v>0.1823090042412521</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3726296282338247</v>
+        <v>0.3683465290587233</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2040070264744111</v>
+        <v>0.2055570264744111</v>
       </c>
       <c r="C89">
-        <v>-7728.37709273524</v>
+        <v>-7884.784968853161</v>
       </c>
       <c r="D89">
-        <v>2823.66690726476</v>
+        <v>2796.271031146839</v>
       </c>
       <c r="E89">
-        <v>5373.544</v>
+        <v>5502.556</v>
       </c>
       <c r="F89">
-        <v>11224.044</v>
+        <v>11353.056</v>
       </c>
       <c r="G89">
         <v>672</v>
@@ -8713,37 +8713,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M89">
-        <v>2253.7880352</v>
+        <v>2279.6936448</v>
       </c>
       <c r="N89">
-        <v>-1423.6130352</v>
+        <v>-1449.5186448</v>
       </c>
       <c r="O89">
-        <v>-355.9032588000001</v>
+        <v>-362.3796612000001</v>
       </c>
       <c r="P89">
-        <v>-1067.7097764</v>
+        <v>-1087.1389836</v>
       </c>
       <c r="Q89">
-        <v>-667.5097764000005</v>
+        <v>-686.9389836000004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3492168675732447</v>
+        <v>0.3745016065376817</v>
       </c>
       <c r="T89">
-        <v>6.081584524995113</v>
+        <v>6.588383235411373</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.09208663226468083</v>
+        <v>0.09104019326167311</v>
       </c>
       <c r="W89">
-        <v>0.1823090042412521</v>
+        <v>0.182519129193056</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3683465290587233</v>
+        <v>0.3641607730466924</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2055570264744111</v>
+        <v>0.2071070264744111</v>
       </c>
       <c r="C90">
-        <v>-7884.784968853161</v>
+        <v>-8040.666350758019</v>
       </c>
       <c r="D90">
-        <v>2796.271031146839</v>
+        <v>2769.401649241982</v>
       </c>
       <c r="E90">
-        <v>5502.556</v>
+        <v>5631.568000000001</v>
       </c>
       <c r="F90">
-        <v>11353.056</v>
+        <v>11482.068</v>
       </c>
       <c r="G90">
         <v>672</v>
@@ -8795,37 +8795,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M90">
-        <v>2279.6936448</v>
+        <v>2305.599254400001</v>
       </c>
       <c r="N90">
-        <v>-1449.5186448</v>
+        <v>-1475.424254400001</v>
       </c>
       <c r="O90">
-        <v>-362.3796612000001</v>
+        <v>-368.8560636000002</v>
       </c>
       <c r="P90">
-        <v>-1087.1389836</v>
+        <v>-1106.568190800001</v>
       </c>
       <c r="Q90">
-        <v>-686.9389836000004</v>
+        <v>-706.3681908000007</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3745016065376817</v>
+        <v>0.4043835707683801</v>
       </c>
       <c r="T90">
-        <v>6.588383235411373</v>
+        <v>7.187327165903317</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.09104019326167311</v>
+        <v>0.090017269741879</v>
       </c>
       <c r="W90">
-        <v>0.182519129193056</v>
+        <v>0.1827245322358307</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3641607730466924</v>
+        <v>0.3600690789675159</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2071070264744111</v>
+        <v>0.2086570264744111</v>
       </c>
       <c r="C91">
-        <v>-8040.666350758019</v>
+        <v>-8196.036271255845</v>
       </c>
       <c r="D91">
-        <v>2769.401649241982</v>
+        <v>2743.043728744155</v>
       </c>
       <c r="E91">
-        <v>5631.568000000001</v>
+        <v>5760.580000000002</v>
       </c>
       <c r="F91">
-        <v>11482.068</v>
+        <v>11611.08</v>
       </c>
       <c r="G91">
         <v>672</v>
@@ -8877,37 +8877,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M91">
-        <v>2305.599254400001</v>
+        <v>2331.504864</v>
       </c>
       <c r="N91">
-        <v>-1475.424254400001</v>
+        <v>-1501.329864000001</v>
       </c>
       <c r="O91">
-        <v>-368.8560636000002</v>
+        <v>-375.3324660000002</v>
       </c>
       <c r="P91">
-        <v>-1106.568190800001</v>
+        <v>-1125.997398</v>
       </c>
       <c r="Q91">
-        <v>-706.3681908000007</v>
+        <v>-725.7973980000005</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4043835707683801</v>
+        <v>0.4402419278452182</v>
       </c>
       <c r="T91">
-        <v>7.187327165903317</v>
+        <v>7.90605988249365</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.090017269741879</v>
+        <v>0.08901707785585813</v>
       </c>
       <c r="W91">
-        <v>0.1827245322358307</v>
+        <v>0.1829253707665437</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3600690789675159</v>
+        <v>0.3560683114234324</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2086570264744111</v>
+        <v>0.2102070264744111</v>
       </c>
       <c r="C92">
-        <v>-8196.036271255845</v>
+        <v>-8350.909196246268</v>
       </c>
       <c r="D92">
-        <v>2743.043728744155</v>
+        <v>2717.182803753732</v>
       </c>
       <c r="E92">
-        <v>5760.580000000002</v>
+        <v>5889.592000000001</v>
       </c>
       <c r="F92">
-        <v>11611.08</v>
+        <v>11740.092</v>
       </c>
       <c r="G92">
         <v>672</v>
@@ -8959,37 +8959,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M92">
-        <v>2331.504864</v>
+        <v>2357.4104736</v>
       </c>
       <c r="N92">
-        <v>-1501.329864000001</v>
+        <v>-1527.235473600001</v>
       </c>
       <c r="O92">
-        <v>-375.3324660000002</v>
+        <v>-381.8088684000002</v>
       </c>
       <c r="P92">
-        <v>-1125.997398</v>
+        <v>-1145.4266052</v>
       </c>
       <c r="Q92">
-        <v>-725.7973980000005</v>
+        <v>-745.2266052000006</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4402419278452182</v>
+        <v>0.4840688087169091</v>
       </c>
       <c r="T92">
-        <v>7.90605988249365</v>
+        <v>8.7845109805485</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08901707785585813</v>
+        <v>0.08803886820909046</v>
       </c>
       <c r="W92">
-        <v>0.1829253707665437</v>
+        <v>0.1831217952636146</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3560683114234324</v>
+        <v>0.3521554728363618</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2102070264744111</v>
+        <v>0.2117570264744111</v>
       </c>
       <c r="C93">
-        <v>-8350.909196246268</v>
+        <v>-8505.299051196374</v>
       </c>
       <c r="D93">
-        <v>2717.182803753732</v>
+        <v>2691.804948803627</v>
       </c>
       <c r="E93">
-        <v>5889.592000000001</v>
+        <v>6018.604000000001</v>
       </c>
       <c r="F93">
-        <v>11740.092</v>
+        <v>11869.104</v>
       </c>
       <c r="G93">
         <v>672</v>
@@ -9041,37 +9041,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M93">
-        <v>2357.4104736</v>
+        <v>2383.3160832</v>
       </c>
       <c r="N93">
-        <v>-1527.235473600001</v>
+        <v>-1553.141083200001</v>
       </c>
       <c r="O93">
-        <v>-381.8088684000002</v>
+        <v>-388.2852708000001</v>
       </c>
       <c r="P93">
-        <v>-1145.4266052</v>
+        <v>-1164.855812400001</v>
       </c>
       <c r="Q93">
-        <v>-745.2266052000006</v>
+        <v>-764.6558124000006</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4840688087169091</v>
+        <v>0.5388524098065228</v>
       </c>
       <c r="T93">
-        <v>8.7845109805485</v>
+        <v>9.882574853117065</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08803886820909046</v>
+        <v>0.08708192398942644</v>
       </c>
       <c r="W93">
-        <v>0.1831217952636146</v>
+        <v>0.1833139496629232</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3521554728363618</v>
+        <v>0.3483276959577057</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2117570264744111</v>
+        <v>0.2133070264744111</v>
       </c>
       <c r="C94">
-        <v>-8505.299051196374</v>
+        <v>-8659.219246144739</v>
       </c>
       <c r="D94">
-        <v>2691.804948803627</v>
+        <v>2666.896753855262</v>
       </c>
       <c r="E94">
-        <v>6018.604000000001</v>
+        <v>6147.616000000002</v>
       </c>
       <c r="F94">
-        <v>11869.104</v>
+        <v>11998.116</v>
       </c>
       <c r="G94">
         <v>672</v>
@@ -9123,37 +9123,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M94">
-        <v>2383.3160832</v>
+        <v>2409.2216928</v>
       </c>
       <c r="N94">
-        <v>-1553.141083200001</v>
+        <v>-1579.046692800001</v>
       </c>
       <c r="O94">
-        <v>-388.2852708000001</v>
+        <v>-394.7616732000001</v>
       </c>
       <c r="P94">
-        <v>-1164.855812400001</v>
+        <v>-1184.2850196</v>
       </c>
       <c r="Q94">
-        <v>-764.6558124000006</v>
+        <v>-784.0850196000005</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5388524098065228</v>
+        <v>0.6092884683503118</v>
       </c>
       <c r="T94">
-        <v>9.882574853117065</v>
+        <v>11.29437126070522</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08708192398942644</v>
+        <v>0.08614555921534658</v>
       </c>
       <c r="W94">
-        <v>0.1833139496629232</v>
+        <v>0.1835019717095584</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3483276959577057</v>
+        <v>0.3445822368613863</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2133070264744111</v>
+        <v>0.2148570264744111</v>
       </c>
       <c r="C95">
-        <v>-8659.219246144739</v>
+        <v>-8812.682699329982</v>
       </c>
       <c r="D95">
-        <v>2666.896753855262</v>
+        <v>2642.445300670019</v>
       </c>
       <c r="E95">
-        <v>6147.616000000002</v>
+        <v>6276.628000000001</v>
       </c>
       <c r="F95">
-        <v>11998.116</v>
+        <v>12127.128</v>
       </c>
       <c r="G95">
         <v>672</v>
@@ -9205,37 +9205,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M95">
-        <v>2409.2216928</v>
+        <v>2435.1273024</v>
       </c>
       <c r="N95">
-        <v>-1579.046692800001</v>
+        <v>-1604.9523024</v>
       </c>
       <c r="O95">
-        <v>-394.7616732000001</v>
+        <v>-401.2380756000001</v>
       </c>
       <c r="P95">
-        <v>-1184.2850196</v>
+        <v>-1203.7142268</v>
       </c>
       <c r="Q95">
-        <v>-784.0850196000005</v>
+        <v>-803.5142268000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6092884683503118</v>
+        <v>0.7032032130753639</v>
       </c>
       <c r="T95">
-        <v>11.29437126070522</v>
+        <v>13.17676647082276</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08614555921534658</v>
+        <v>0.0852291170960344</v>
       </c>
       <c r="W95">
-        <v>0.1835019717095584</v>
+        <v>0.1836859932871163</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3445822368613863</v>
+        <v>0.3409164683841375</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2148570264744111</v>
+        <v>0.2164070264744112</v>
       </c>
       <c r="C96">
-        <v>-8812.682699329982</v>
+        <v>-8965.701859531284</v>
       </c>
       <c r="D96">
-        <v>2642.445300670019</v>
+        <v>2618.438140468717</v>
       </c>
       <c r="E96">
-        <v>6276.628000000001</v>
+        <v>6405.640000000001</v>
       </c>
       <c r="F96">
-        <v>12127.128</v>
+        <v>12256.14</v>
       </c>
       <c r="G96">
         <v>672</v>
@@ -9287,37 +9287,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M96">
-        <v>2435.1273024</v>
+        <v>2461.032912</v>
       </c>
       <c r="N96">
-        <v>-1604.9523024</v>
+        <v>-1630.857912</v>
       </c>
       <c r="O96">
-        <v>-401.2380756000001</v>
+        <v>-407.7144780000001</v>
       </c>
       <c r="P96">
-        <v>-1203.7142268</v>
+        <v>-1223.143434</v>
       </c>
       <c r="Q96">
-        <v>-803.5142268000003</v>
+        <v>-822.9434340000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7032032130753639</v>
+        <v>0.8346838556904373</v>
       </c>
       <c r="T96">
-        <v>13.17676647082276</v>
+        <v>15.81211976498732</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.0852291170960344</v>
+        <v>0.0843319684950235</v>
       </c>
       <c r="W96">
-        <v>0.1836859932871163</v>
+        <v>0.1838661407261993</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3409164683841375</v>
+        <v>0.337327873980094</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2164070264744112</v>
+        <v>0.2179570264744111</v>
       </c>
       <c r="C97">
-        <v>-8965.701859531284</v>
+        <v>-9118.288727202047</v>
       </c>
       <c r="D97">
-        <v>2618.438140468717</v>
+        <v>2594.863272797955</v>
       </c>
       <c r="E97">
-        <v>6405.640000000001</v>
+        <v>6534.652000000002</v>
       </c>
       <c r="F97">
-        <v>12256.14</v>
+        <v>12385.152</v>
       </c>
       <c r="G97">
         <v>672</v>
@@ -9369,37 +9369,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M97">
-        <v>2461.032912</v>
+        <v>2486.938521600001</v>
       </c>
       <c r="N97">
-        <v>-1630.857912</v>
+        <v>-1656.763521600001</v>
       </c>
       <c r="O97">
-        <v>-407.7144780000001</v>
+        <v>-414.1908804000002</v>
       </c>
       <c r="P97">
-        <v>-1223.143434</v>
+        <v>-1242.572641200001</v>
       </c>
       <c r="Q97">
-        <v>-822.9434340000004</v>
+        <v>-842.3726412000007</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8346838556904373</v>
+        <v>1.031904819613047</v>
       </c>
       <c r="T97">
-        <v>15.81211976498732</v>
+        <v>19.76514970623415</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.0843319684950235</v>
+        <v>0.08345351048986699</v>
       </c>
       <c r="W97">
-        <v>0.1838661407261993</v>
+        <v>0.1840425350936347</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.337327873980094</v>
+        <v>0.333814041959468</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2179570264744111</v>
+        <v>0.2195070264744111</v>
       </c>
       <c r="C98">
-        <v>-9118.288727202047</v>
+        <v>-9270.454874472129</v>
       </c>
       <c r="D98">
-        <v>2594.863272797953</v>
+        <v>2571.709125527871</v>
       </c>
       <c r="E98">
-        <v>6534.652</v>
+        <v>6663.664000000001</v>
       </c>
       <c r="F98">
-        <v>12385.152</v>
+        <v>12514.164</v>
       </c>
       <c r="G98">
         <v>672</v>
@@ -9451,37 +9451,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M98">
-        <v>2486.9385216</v>
+        <v>2512.8441312</v>
       </c>
       <c r="N98">
-        <v>-1656.7635216</v>
+        <v>-1682.6691312</v>
       </c>
       <c r="O98">
-        <v>-414.1908804000001</v>
+        <v>-420.6672828000001</v>
       </c>
       <c r="P98">
-        <v>-1242.5726412</v>
+        <v>-1262.0018484</v>
       </c>
       <c r="Q98">
-        <v>-842.3726412000004</v>
+        <v>-861.8018484000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.031904819613044</v>
+        <v>1.360606426150726</v>
       </c>
       <c r="T98">
-        <v>19.7651497062341</v>
+        <v>26.35353294164547</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08345351048986702</v>
+        <v>0.08259316502089931</v>
       </c>
       <c r="W98">
-        <v>0.1840425350936347</v>
+        <v>0.1842152924638034</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.333814041959468</v>
+        <v>0.3303726600835972</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2195070264744111</v>
+        <v>0.2210570264744111</v>
       </c>
       <c r="C99">
-        <v>-9270.454874472129</v>
+        <v>-9422.21146408863</v>
       </c>
       <c r="D99">
-        <v>2571.709125527871</v>
+        <v>2548.964535911371</v>
       </c>
       <c r="E99">
-        <v>6663.664000000001</v>
+        <v>6792.676000000001</v>
       </c>
       <c r="F99">
-        <v>12514.164</v>
+        <v>12643.176</v>
       </c>
       <c r="G99">
         <v>672</v>
@@ -9533,37 +9533,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M99">
-        <v>2512.8441312</v>
+        <v>2538.7497408</v>
       </c>
       <c r="N99">
-        <v>-1682.6691312</v>
+        <v>-1708.574740800001</v>
       </c>
       <c r="O99">
-        <v>-420.6672828000001</v>
+        <v>-427.1436852000002</v>
       </c>
       <c r="P99">
-        <v>-1262.0018484</v>
+        <v>-1281.4310556</v>
       </c>
       <c r="Q99">
-        <v>-861.8018484000003</v>
+        <v>-881.2310556000006</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.360606426150726</v>
+        <v>2.018009639226088</v>
       </c>
       <c r="T99">
-        <v>26.35353294164547</v>
+        <v>39.5302994124682</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08259316502089931</v>
+        <v>0.08175037762272686</v>
       </c>
       <c r="W99">
-        <v>0.1842152924638034</v>
+        <v>0.1843845241733565</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3303726600835972</v>
+        <v>0.3270015104909074</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2210570264744111</v>
+        <v>0.2226070264744112</v>
       </c>
       <c r="C100">
-        <v>-9422.21146408863</v>
+        <v>-9573.569267360392</v>
       </c>
       <c r="D100">
-        <v>2548.964535911371</v>
+        <v>2526.618732639609</v>
       </c>
       <c r="E100">
-        <v>6792.676000000001</v>
+        <v>6921.688</v>
       </c>
       <c r="F100">
-        <v>12643.176</v>
+        <v>12772.188</v>
       </c>
       <c r="G100">
         <v>672</v>
@@ -9615,37 +9615,37 @@
         <v>830.1749999999998</v>
       </c>
       <c r="M100">
-        <v>2538.7497408</v>
+        <v>2564.6553504</v>
       </c>
       <c r="N100">
-        <v>-1708.574740800001</v>
+        <v>-1734.480350400001</v>
       </c>
       <c r="O100">
-        <v>-427.1436852000002</v>
+        <v>-433.6200876000001</v>
       </c>
       <c r="P100">
-        <v>-1281.4310556</v>
+        <v>-1300.8602628</v>
       </c>
       <c r="Q100">
-        <v>-881.2310556000006</v>
+        <v>-900.6602628000004</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.018009639226088</v>
+        <v>3.990219278452177</v>
       </c>
       <c r="T100">
-        <v>39.5302994124682</v>
+        <v>79.06059882493641</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.08175037762272686</v>
+        <v>0.08092461623259831</v>
       </c>
       <c r="W100">
-        <v>0.1843845241733565</v>
+        <v>0.1845503370604943</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3270015104909074</v>
+        <v>0.3236984649303932</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2226070264744112</v>
-      </c>
-      <c r="C101">
-        <v>-9573.569267360392</v>
-      </c>
-      <c r="D101">
-        <v>2526.618732639609</v>
-      </c>
-      <c r="E101">
-        <v>6921.688</v>
-      </c>
-      <c r="F101">
-        <v>12772.188</v>
-      </c>
-      <c r="G101">
-        <v>672</v>
-      </c>
-      <c r="H101">
-        <v>7050.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1230.375</v>
-      </c>
-      <c r="K101">
-        <v>400.1999999999999</v>
-      </c>
-      <c r="L101">
-        <v>830.1749999999998</v>
-      </c>
-      <c r="M101">
-        <v>2564.6553504</v>
-      </c>
-      <c r="N101">
-        <v>-1734.480350400001</v>
-      </c>
-      <c r="O101">
-        <v>-433.6200876000001</v>
-      </c>
-      <c r="P101">
-        <v>-1300.8602628</v>
-      </c>
-      <c r="Q101">
-        <v>-900.6602628000004</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.990219278452177</v>
-      </c>
-      <c r="T101">
-        <v>79.06059882493641</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.08092461623259831</v>
-      </c>
-      <c r="W101">
-        <v>0.1845503370604943</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3236984649303932</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
